--- a/排课结果/失败课程归因与建议.xlsx
+++ b/排课结果/失败课程归因与建议.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O241"/>
+  <dimension ref="A1:P241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,11 @@
           <t>枚举拒绝构成</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>软偏好修复结果</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -569,6 +574,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -646,6 +652,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -723,6 +730,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -800,6 +808,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -877,6 +886,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -954,6 +964,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1031,6 +1042,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1108,6 +1120,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1185,6 +1198,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1262,6 +1276,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1339,6 +1354,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1416,6 +1432,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1493,6 +1510,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1570,6 +1588,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1647,6 +1666,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1724,6 +1744,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1801,6 +1822,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1878,6 +1900,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1955,6 +1978,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2032,6 +2056,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2109,6 +2134,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2186,6 +2212,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2263,6 +2290,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2340,6 +2368,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2417,6 +2446,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2494,6 +2524,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2571,6 +2602,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2648,6 +2680,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2725,6 +2758,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2802,6 +2836,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2879,6 +2914,11 @@
           <t>偏好窗口外×44；教室占用×9；教师占用×2</t>
         </is>
       </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>✅已由软偏好修复排入 周三第7-8节</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2956,6 +2996,7 @@
           <t>偏好窗口外×236；教师占用×38；教室占用×21</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3033,6 +3074,7 @@
           <t>偏好窗口外×236；教师占用×32；教室占用×27</t>
         </is>
       </c>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3110,6 +3152,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3187,6 +3230,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3264,6 +3308,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3341,6 +3386,11 @@
           <t>偏好窗口外×236；教师占用×40；教室占用×19</t>
         </is>
       </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>✅已由软偏好修复排入 周五第7-8节</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3418,6 +3468,11 @@
           <t>偏好窗口外×236；教师占用×38；教室占用×21</t>
         </is>
       </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>✅已由软偏好修复排入 周四第7-8节</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3491,6 +3546,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3568,6 +3624,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3645,6 +3702,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3722,6 +3780,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3799,6 +3858,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3876,6 +3936,7 @@
           <t>偏好窗口外×1415</t>
         </is>
       </c>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3953,6 +4014,11 @@
           <t>偏好窗口外×956；教室占用×136；教师占用×103</t>
         </is>
       </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>✅已由软偏好修复排入 周五第3-4节</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4030,6 +4096,11 @@
           <t>偏好窗口外×236；教师占用×31；教室占用×28</t>
         </is>
       </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>✅已由软偏好修复排入 周一第3-4节</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4107,6 +4178,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4184,6 +4256,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4261,6 +4334,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4338,6 +4412,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4415,6 +4490,7 @@
           <t>偏好窗口外×44；禁止时段×11</t>
         </is>
       </c>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4492,6 +4568,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4569,6 +4646,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4646,6 +4724,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4723,6 +4802,7 @@
           <t>偏好窗口外×44；禁止时段×11</t>
         </is>
       </c>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4800,6 +4880,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4877,6 +4958,7 @@
           <t>偏好窗口外×44；禁止时段×11</t>
         </is>
       </c>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4954,6 +5036,7 @@
           <t>偏好窗口外×44；禁止时段×11</t>
         </is>
       </c>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5031,6 +5114,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5108,6 +5192,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5185,6 +5270,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5262,6 +5348,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5339,6 +5426,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5416,6 +5504,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5493,6 +5582,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5570,6 +5660,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5647,6 +5738,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5724,6 +5816,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5801,6 +5894,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5878,6 +5972,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5955,6 +6050,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6032,6 +6128,7 @@
           <t>偏好窗口外×55</t>
         </is>
       </c>
+      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6109,6 +6206,7 @@
           <t>偏好窗口外×55</t>
         </is>
       </c>
+      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6186,6 +6284,7 @@
           <t>偏好窗口外×55</t>
         </is>
       </c>
+      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6263,6 +6362,7 @@
           <t>偏好窗口外×55</t>
         </is>
       </c>
+      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6340,6 +6440,7 @@
           <t>偏好窗口外×55</t>
         </is>
       </c>
+      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6417,6 +6518,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6494,6 +6596,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6571,6 +6674,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6648,6 +6752,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6725,6 +6830,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6802,6 +6908,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6879,6 +6986,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6956,6 +7064,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7033,6 +7142,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7110,6 +7220,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7187,6 +7298,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7264,6 +7376,7 @@
           <t>偏好窗口外×44；禁止时段×11</t>
         </is>
       </c>
+      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7341,6 +7454,7 @@
           <t>偏好窗口外×44；禁止时段×11</t>
         </is>
       </c>
+      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7418,6 +7532,7 @@
           <t>偏好窗口外×44；禁止时段×11</t>
         </is>
       </c>
+      <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7495,6 +7610,7 @@
           <t>偏好窗口外×44；禁止时段×11</t>
         </is>
       </c>
+      <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7572,6 +7688,7 @@
           <t>偏好窗口外×44；禁止时段×11</t>
         </is>
       </c>
+      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7649,6 +7766,11 @@
           <t>偏好窗口外×236；教师占用×38；教室占用×21</t>
         </is>
       </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>✅已由软偏好修复排入 周四第5-6节</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7726,6 +7848,11 @@
           <t>偏好窗口外×236；教师占用×38；教室占用×21</t>
         </is>
       </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>✅已由软偏好修复排入 周四第5-6节</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7803,6 +7930,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7880,6 +8008,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7957,6 +8086,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8034,6 +8164,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8111,6 +8242,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8188,6 +8320,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8265,6 +8398,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8342,6 +8476,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8419,6 +8554,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8496,6 +8632,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8573,6 +8710,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -8650,6 +8788,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8727,6 +8866,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8804,6 +8944,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8881,6 +9022,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8958,6 +9100,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9035,6 +9178,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9112,6 +9256,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9189,6 +9334,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9266,6 +9412,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -9343,6 +9490,7 @@
           <t>偏好窗口外×236；禁止时段×59</t>
         </is>
       </c>
+      <c r="P116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -9420,6 +9568,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -9497,6 +9646,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -9574,6 +9724,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -9651,6 +9802,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -9728,6 +9880,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -9805,6 +9958,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -9882,6 +10036,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -9959,6 +10114,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10036,6 +10192,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10113,6 +10270,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10190,6 +10348,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10267,6 +10426,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10344,6 +10504,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -10421,6 +10582,7 @@
           <t>偏好窗口外×295</t>
         </is>
       </c>
+      <c r="P130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10490,6 +10652,7 @@
       </c>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -10559,6 +10722,7 @@
       </c>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -10628,6 +10792,7 @@
       </c>
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -10697,6 +10862,7 @@
       </c>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -10766,6 +10932,7 @@
       </c>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -10835,6 +11002,7 @@
       </c>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -10900,6 +11068,7 @@
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -10969,6 +11138,7 @@
       </c>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -11038,6 +11208,7 @@
       </c>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -11107,6 +11278,7 @@
       </c>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -11172,6 +11344,7 @@
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -11241,6 +11414,7 @@
       </c>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -11310,6 +11484,7 @@
       </c>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -11379,6 +11554,7 @@
       </c>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -11444,6 +11620,7 @@
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -11513,6 +11690,7 @@
       </c>
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -11582,6 +11760,7 @@
       </c>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -11651,6 +11830,7 @@
       </c>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -11720,6 +11900,7 @@
       </c>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -11789,6 +11970,7 @@
       </c>
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -11858,6 +12040,7 @@
       </c>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -11927,6 +12110,7 @@
       </c>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -11996,6 +12180,7 @@
       </c>
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -12065,6 +12250,7 @@
       </c>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -12134,6 +12320,7 @@
       </c>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -12203,6 +12390,7 @@
       </c>
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -12272,6 +12460,7 @@
       </c>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -12341,6 +12530,7 @@
       </c>
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -12410,6 +12600,7 @@
       </c>
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -12479,6 +12670,7 @@
       </c>
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -12548,6 +12740,7 @@
       </c>
       <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -12617,6 +12810,7 @@
       </c>
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -12682,6 +12876,7 @@
       <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -12751,6 +12946,7 @@
       </c>
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -12820,6 +13016,7 @@
       </c>
       <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -12889,6 +13086,7 @@
       </c>
       <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -12958,6 +13156,7 @@
       </c>
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -13027,6 +13226,7 @@
       </c>
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -13096,6 +13296,7 @@
       </c>
       <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -13165,6 +13366,7 @@
       </c>
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -13234,6 +13436,7 @@
       </c>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -13303,6 +13506,7 @@
       </c>
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -13372,6 +13576,7 @@
       </c>
       <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -13441,6 +13646,7 @@
       </c>
       <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -13510,6 +13716,7 @@
       </c>
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -13579,6 +13786,7 @@
       </c>
       <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -13648,6 +13856,7 @@
       </c>
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -13717,6 +13926,7 @@
       </c>
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -13786,6 +13996,7 @@
       </c>
       <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -13859,6 +14070,7 @@
           <t>班级占用×586；分段/连排边界×145；教室占用×81；禁止时段×58</t>
         </is>
       </c>
+      <c r="P180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -13924,6 +14136,7 @@
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -13997,6 +14210,7 @@
           <t>班级占用×601；分段/连排边界×145；教室占用×66；禁止时段×58</t>
         </is>
       </c>
+      <c r="P182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -14066,6 +14280,7 @@
       </c>
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
+      <c r="P183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -14131,6 +14346,7 @@
       <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -14200,6 +14416,7 @@
       </c>
       <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr"/>
+      <c r="P185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -14269,6 +14486,7 @@
       </c>
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
+      <c r="P186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -14338,6 +14556,7 @@
       </c>
       <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr"/>
+      <c r="P187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -14403,6 +14622,7 @@
       <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -14472,6 +14692,7 @@
       </c>
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
+      <c r="P189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -14549,6 +14770,7 @@
           <t>偏好窗口外×1195</t>
         </is>
       </c>
+      <c r="P190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -14618,6 +14840,7 @@
       </c>
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -14687,6 +14910,7 @@
       </c>
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -14756,6 +14980,7 @@
       </c>
       <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -14825,6 +15050,7 @@
       </c>
       <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -14894,6 +15120,7 @@
       </c>
       <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -14959,6 +15186,7 @@
       <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -15028,6 +15256,7 @@
       </c>
       <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -15097,6 +15326,7 @@
       </c>
       <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -15166,6 +15396,7 @@
       </c>
       <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -15235,6 +15466,7 @@
       </c>
       <c r="N200" t="inlineStr"/>
       <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -15304,6 +15536,7 @@
       </c>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -15373,6 +15606,7 @@
       </c>
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -15450,6 +15684,7 @@
           <t>偏好窗口外×1195</t>
         </is>
       </c>
+      <c r="P203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -15527,6 +15762,7 @@
           <t>偏好窗口外×1195</t>
         </is>
       </c>
+      <c r="P204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -15600,6 +15836,7 @@
           <t>偏好窗口外×1810</t>
         </is>
       </c>
+      <c r="P205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -15677,6 +15914,7 @@
           <t>偏好窗口外×1980</t>
         </is>
       </c>
+      <c r="P206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -15754,6 +15992,7 @@
           <t>偏好窗口外×1980</t>
         </is>
       </c>
+      <c r="P207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -15831,6 +16070,7 @@
           <t>偏好窗口外×1980</t>
         </is>
       </c>
+      <c r="P208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -15908,6 +16148,7 @@
           <t>偏好窗口外×1985</t>
         </is>
       </c>
+      <c r="P209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -15985,6 +16226,7 @@
           <t>偏好窗口外×1985</t>
         </is>
       </c>
+      <c r="P210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -16062,6 +16304,7 @@
           <t>偏好窗口外×1985</t>
         </is>
       </c>
+      <c r="P211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -16139,6 +16382,7 @@
           <t>偏好窗口外×1965</t>
         </is>
       </c>
+      <c r="P212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -16208,6 +16452,7 @@
       </c>
       <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -16277,6 +16522,7 @@
       </c>
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr"/>
+      <c r="P214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -16346,6 +16592,7 @@
       </c>
       <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr"/>
+      <c r="P215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -16415,6 +16662,7 @@
       </c>
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr"/>
+      <c r="P216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -16484,6 +16732,7 @@
       </c>
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr"/>
+      <c r="P217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -16553,6 +16802,7 @@
       </c>
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr"/>
+      <c r="P218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -16618,6 +16868,7 @@
       <c r="M219" t="inlineStr"/>
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
+      <c r="P219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -16695,6 +16946,7 @@
           <t>偏好窗口外×540；教室占用×204；教师占用×66</t>
         </is>
       </c>
+      <c r="P220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -16772,6 +17024,7 @@
           <t>偏好窗口外×540；教室占用×204；教师占用×66</t>
         </is>
       </c>
+      <c r="P221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -16849,6 +17102,7 @@
           <t>偏好窗口外×540；教室占用×204；教师占用×66</t>
         </is>
       </c>
+      <c r="P222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -16926,6 +17180,7 @@
           <t>偏好窗口外×540；教室占用×204；教师占用×66</t>
         </is>
       </c>
+      <c r="P223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -17003,6 +17258,7 @@
           <t>偏好窗口外×540；教室占用×204；教师占用×66</t>
         </is>
       </c>
+      <c r="P224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -17080,6 +17336,7 @@
           <t>偏好窗口外×540；教室占用×204；教师占用×66</t>
         </is>
       </c>
+      <c r="P225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -17157,6 +17414,7 @@
           <t>偏好窗口外×540；教室占用×204；教师占用×66</t>
         </is>
       </c>
+      <c r="P226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -17234,6 +17492,7 @@
           <t>偏好窗口外×540；教室占用×204；教师占用×66</t>
         </is>
       </c>
+      <c r="P227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -17311,6 +17570,7 @@
           <t>偏好窗口外×540；教室占用×204；教师占用×66</t>
         </is>
       </c>
+      <c r="P228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -17388,6 +17648,7 @@
           <t>偏好窗口外×540；教室占用×204；教师占用×66</t>
         </is>
       </c>
+      <c r="P229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -17465,6 +17726,7 @@
           <t>偏好窗口外×540；教室占用×204；教师占用×66</t>
         </is>
       </c>
+      <c r="P230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -17542,6 +17804,7 @@
           <t>偏好窗口外×405；教室占用×202；教师占用×68</t>
         </is>
       </c>
+      <c r="P231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -17619,6 +17882,7 @@
           <t>偏好窗口外×405；教室占用×202；教师占用×68</t>
         </is>
       </c>
+      <c r="P232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -17696,6 +17960,7 @@
           <t>偏好窗口外×405；教室占用×202；教师占用×68</t>
         </is>
       </c>
+      <c r="P233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -17773,6 +18038,7 @@
           <t>偏好窗口外×18；教室占用×12</t>
         </is>
       </c>
+      <c r="P234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -17850,6 +18116,7 @@
           <t>偏好窗口外×540；教室占用×204；教师占用×66</t>
         </is>
       </c>
+      <c r="P235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -17927,6 +18194,7 @@
           <t>偏好窗口外×540；教室占用×204；教师占用×66</t>
         </is>
       </c>
+      <c r="P236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -18004,6 +18272,7 @@
           <t>偏好窗口外×540；教室占用×204；教师占用×66</t>
         </is>
       </c>
+      <c r="P237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -18081,6 +18350,7 @@
           <t>偏好窗口外×540；教室占用×204；教师占用×66</t>
         </is>
       </c>
+      <c r="P238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -18146,6 +18416,7 @@
       <c r="M239" t="inlineStr"/>
       <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr"/>
+      <c r="P239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -18211,6 +18482,7 @@
       <c r="M240" t="inlineStr"/>
       <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr"/>
+      <c r="P240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -18276,6 +18548,7 @@
       <c r="M241" t="inlineStr"/>
       <c r="N241" t="inlineStr"/>
       <c r="O241" t="inlineStr"/>
+      <c r="P241" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/排课结果/失败课程归因与建议.xlsx
+++ b/排课结果/失败课程归因与建议.xlsx
@@ -2996,7 +2996,11 @@
           <t>偏好窗口外×236；教师占用×38；教室占用×21</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>✅已由软偏好修复排入 周四第5-6节</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3074,7 +3078,11 @@
           <t>偏好窗口外×236；教师占用×32；教室占用×27</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>✅已由软偏好修复排入 周四第7-8节</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">

--- a/排课结果/失败课程归因与建议.xlsx
+++ b/排课结果/失败课程归因与建议.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P232"/>
+  <dimension ref="A1:P230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12349,11 +12349,7 @@
           <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
         </is>
       </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>新海(xkp01090132): 第13教学周已占1节; 第14教学周已占1节</t>
-        </is>
-      </c>
+      <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
@@ -13271,7 +13267,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>62221001.001</t>
+          <t>62221001.002</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13286,81 +13282,77 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=210.0</t>
+          <t>课程行校区=北校区 | 课容量=210.0</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>资源冲突或偏好过窄</t>
+          <t>教室静态不可行</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>④ 班级时段冲突</t>
+          <t>⓪ 教室预筛</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>班级时段冲突(学生班级在偏好时段已有课)</t>
+          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Prefer=无</t>
+          <t>ZXS=2.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>调整班级课表 / 放宽偏好窗口</t>
+          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>一级</t>
+          <t>二级</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：班级占用。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=203（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=667（教室/教师/班级）。 累计资源拒绝更高，更说明在现行时间规则下栅格冲突偏紧（教室或师生占用）。 资源侧枚举构成：班级占用×414；教室占用×253。</t>
+          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
-        </is>
-      </c>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>班级占用</t>
-        </is>
-      </c>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>班级占用×414；教室占用×253；分段/连排边界×145；禁止时段×58</t>
-        </is>
-      </c>
+          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>新蒙(xkp01231016): 第9教学周已占2节; 第10教学周已占2节</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>62221001.002</t>
+          <t>081010790.001</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>侦探之旅：从柯南道尔到AI司鉴</t>
+          <t>高电压技术</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=5.5</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>课程行校区=北校区 | 课容量=210.0</t>
+          <t>课程行校区=南校区 | 课容量=304.0 | 教室类型名称=固定桌椅多媒体</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -13380,7 +13372,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>ZXS=2.0 | Prefer=无</t>
+          <t>ZXS=5.5 | Prefer=无</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -13403,7 +13395,11 @@
           <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
         </is>
       </c>
-      <c r="M172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>新来军(xkp01060067): 第6教学周已占6节; 第7教学周已占6节</t>
+        </is>
+      </c>
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr"/>
@@ -13411,47 +13407,47 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>62251003.001</t>
+          <t>081010810.001</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>数字时代的感官养护</t>
+          <t>现代电气控制技术与PLC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=210.0</t>
+          <t>课程行校区=南校区 | 课容量=270.0 | 教室类型名称=固定桌椅多媒体</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>启发式未选中或其它</t>
+          <t>教室静态不可行</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>⓪ 其它</t>
+          <t>⓪ 教室预筛</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>其它资源叠加冲突</t>
+          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>拒绝构成={}</t>
+          <t>ZXS=4.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>结合枚举拒绝构成与教师占用摘要逐项排查</t>
+          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -13461,12 +13457,12 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>静态枚举最大方案数&gt;0（严格 1 / 放宽 1），仍失败可能与排课顺序、批量终止等有关</t>
+          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>调整排课顺序、分批策略或运行调课；结合排课前检查模块复核偏好</t>
+          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
         </is>
       </c>
       <c r="M173" t="inlineStr"/>
@@ -13477,22 +13473,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>081010790.001</t>
+          <t>090010740.002</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>高电压技术</t>
+          <t>大数据分析技术</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=5.5</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=304.0 | 教室类型名称=固定桌椅多媒体</t>
+          <t>课程行校区=北校区 | 课容量=204.0</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -13512,7 +13508,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>ZXS=5.5 | Prefer=无</t>
+          <t>ZXS=4.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -13537,7 +13533,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>新来军(xkp01060067): 第6教学周已占6节; 第7教学周已占6节</t>
+          <t>新朝生(xkp01070108): 第7教学周已占8节; 第8教学周已占8节</t>
         </is>
       </c>
       <c r="N174" t="inlineStr"/>
@@ -13547,12 +13543,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>081010810.001</t>
+          <t>091010020.001</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>现代电气控制技术与PLC</t>
+          <t>算法分析与设计</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -13562,7 +13558,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=270.0 | 教室类型名称=固定桌椅多媒体</t>
+          <t>课程行校区=北校区 | 课容量=245.0</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -13605,7 +13601,11 @@
           <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
         </is>
       </c>
-      <c r="M175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>新东(xkp01079355): 第9教学周已占8节; 第10教学周已占8节</t>
+        </is>
+      </c>
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
@@ -13613,12 +13613,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>090010740.002</t>
+          <t>091017031.001</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>大数据分析技术</t>
+          <t>文献检索与科技论文写作</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -13673,7 +13673,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>新朝生(xkp01070108): 第7教学周已占8节; 第8教学周已占8节</t>
+          <t>新富凯(xkp01230450): 第13教学周已占8节; 第14教学周已占8节</t>
         </is>
       </c>
       <c r="N176" t="inlineStr"/>
@@ -13683,12 +13683,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>091010020.001</t>
+          <t>091058011.001</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>算法分析与设计</t>
+          <t>软件新技术讲座</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -13698,7 +13698,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>课程行校区=北校区 | 课容量=245.0</t>
+          <t>课程行校区=北校区 | 课容量=204.0</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -13741,11 +13741,7 @@
           <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
         </is>
       </c>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>新东(xkp01079355): 第9教学周已占8节; 第10教学周已占8节</t>
-        </is>
-      </c>
+      <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr"/>
@@ -13753,67 +13749,67 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>091017031.001</t>
+          <t>110010321.001</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>文献检索与科技论文写作</t>
+          <t>高等代数2</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
+          <t>Prefer_Time=周六全天；周日全天 | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=2条 | 禁止时段解析块=1段 | ZXS=8.0</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>课程行校区=北校区 | 课容量=204.0</t>
+          <t>课程行校区=南校区 | 课容量=100.0 | 教室类型名称=固定桌椅多媒体</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>教室静态不可行</t>
+          <t>时间偏好与周学时</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>⓪ 教室预筛</t>
+          <t>⓪ 日模式生成</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
+          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>ZXS=4.0 | Prefer=无</t>
+          <t>ZXS=8.0 | Prefer=周六全天;周日全天 | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
+          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>二级</t>
+          <t>一级</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
+          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
+          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>新富凯(xkp01230450): 第13教学周已占8节; 第14教学周已占8节</t>
+          <t>新杰(xkp01040124): 第3教学周已占10节; 第4教学周已占10节</t>
         </is>
       </c>
       <c r="N178" t="inlineStr"/>
@@ -13823,88 +13819,100 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>091058011.001</t>
+          <t>150010280.001</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>软件新技术讲座</t>
+          <t>运动处方理论与应用</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
+          <t>Prefer_Time=周五（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=1.9999999</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>课程行校区=北校区 | 课容量=204.0</t>
+          <t>课程行校区=南校区 | 课容量=82.0</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>教室静态不可行</t>
+          <t>资源冲突或偏好过窄</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>⓪ 教室预筛</t>
+          <t>① 偏好节次错位</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
+          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>ZXS=4.0 | Prefer=无</t>
+          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
+          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>二级</t>
+          <t>一级</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1195（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新燚(xkp01050067): 第1教学周已占4节; 第2教学周已占4节</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
-        </is>
-      </c>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
-      <c r="O179" t="inlineStr"/>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>新燚(xkp01050067): 第1教学周已占4节; 第2教学周已占4节</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>偏好窗口外</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>偏好窗口外×1195</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>110010321.001</t>
+          <t>150130580.002</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>高等代数2</t>
+          <t>专项4</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Prefer_Time=周六全天；周日全天 | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=2条 | 禁止时段解析块=1段 | ZXS=8.0</t>
+          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=100.0 | 教室类型名称=固定桌椅多媒体</t>
+          <t>课程行校区=南校区 | 课容量=7.0</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -13924,7 +13932,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>ZXS=8.0 | Prefer=周六全天;周日全天 | unavail=周二(5-8节)</t>
+          <t>ZXS=6.0 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -13949,7 +13957,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>新杰(xkp01040124): 第3教学周已占10节; 第4教学周已占10节</t>
+          <t>新建营(xkp01050033): 第1教学周已占10节; 第2教学周已占16节</t>
         </is>
       </c>
       <c r="N180" t="inlineStr"/>
@@ -13959,47 +13967,47 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>150010280.001</t>
+          <t>150130580.003</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>运动处方理论与应用</t>
+          <t>专项4</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Prefer_Time=周五（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=1.9999999</t>
+          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=82.0</t>
+          <t>课程行校区=南校区 | 课容量=14.0</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>资源冲突或偏好过窄</t>
+          <t>时间偏好与周学时</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>① 偏好节次错位</t>
+          <t>⓪ 日模式生成</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
+          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
+          <t>ZXS=6.0 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
+          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -14009,35 +14017,27 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1195（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新燚(xkp01050067): 第1教学周已占4节; 第2教学周已占4节</t>
+          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
+          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>新燚(xkp01050067): 第1教学周已占4节; 第2教学周已占4节</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr">
-        <is>
-          <t>偏好窗口外</t>
-        </is>
-      </c>
-      <c r="O181" t="inlineStr">
-        <is>
-          <t>偏好窗口外×1195</t>
-        </is>
-      </c>
+          <t>新毅新(xkp01050084): 第1教学周已占10节; 第2教学周已占10节</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>150130580.002</t>
+          <t>150130580.004</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=7.0</t>
+          <t>课程行校区=南校区 | 课容量=14.0</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -14097,7 +14097,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>新建营(xkp01050033): 第1教学周已占10节; 第2教学周已占16节</t>
+          <t>新军勇(xkp01050009): 第1教学周已占10节; 第2教学周已占10节</t>
         </is>
       </c>
       <c r="N182" t="inlineStr"/>
@@ -14107,7 +14107,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>150130580.003</t>
+          <t>150130580.005</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14167,7 +14167,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>新毅新(xkp01050084): 第1教学周已占10节; 第2教学周已占10节</t>
+          <t>新希丹(xkp01050079): 第1教学周已占2节; 第2教学周已占8节</t>
         </is>
       </c>
       <c r="N183" t="inlineStr"/>
@@ -14177,7 +14177,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>150130580.004</t>
+          <t>150130580.006</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14187,12 +14187,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
+          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=5.5</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=14.0</t>
+          <t>课程行校区=南校区 | 课容量=13.0</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>ZXS=6.0 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
+          <t>ZXS=5.5 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>新军勇(xkp01050009): 第1教学周已占10节; 第2教学周已占10节</t>
+          <t>新艳华(xkp01050031): 第1教学周已占4节; 第2教学周已占10节</t>
         </is>
       </c>
       <c r="N184" t="inlineStr"/>
@@ -14247,7 +14247,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>150130580.005</t>
+          <t>150130580.007</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=14.0</t>
+          <t>课程行校区=南校区 | 课容量=13.0</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -14305,11 +14305,7 @@
           <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
         </is>
       </c>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>新希丹(xkp01050079): 第1教学周已占2节; 第2教学周已占8节</t>
-        </is>
-      </c>
+      <c r="M185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr"/>
@@ -14317,7 +14313,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>150130580.006</t>
+          <t>150130580.008</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14327,12 +14323,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=5.5</t>
+          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=13.0</t>
+          <t>课程行校区=南校区 | 课容量=14.0</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -14352,7 +14348,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>ZXS=5.5 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
+          <t>ZXS=6.0 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -14377,7 +14373,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>新艳华(xkp01050031): 第1教学周已占4节; 第2教学周已占10节</t>
+          <t>新爱增(xkp01230004): 第1教学周已占2节; 第2教学周已占2节</t>
         </is>
       </c>
       <c r="N186" t="inlineStr"/>
@@ -14387,12 +14383,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>150130580.007</t>
+          <t>150130680.002</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>专项2</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -14402,7 +14398,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=13.0</t>
+          <t>课程行校区=南校区 | 课容量=11.0</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -14445,7 +14441,11 @@
           <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
         </is>
       </c>
-      <c r="M187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>新正龙(xkp01050039): 第1教学周已占6节; 第2教学周已占18节</t>
+        </is>
+      </c>
       <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr"/>
@@ -14453,12 +14453,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>150130580.008</t>
+          <t>150130680.003</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>专项2</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=14.0</t>
+          <t>课程行校区=南校区 | 课容量=11.0</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -14513,7 +14513,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>新爱增(xkp01230004): 第1教学周已占2节; 第2教学周已占2节</t>
+          <t>新海兵(xkp01050014): 第1教学周已占8节; 第2教学周已占8节</t>
         </is>
       </c>
       <c r="N188" t="inlineStr"/>
@@ -14523,7 +14523,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>150130680.002</t>
+          <t>150130680.004</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14533,12 +14533,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
+          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=11.0</t>
+          <t>课程行校区=南校区 | 课容量=10.0</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>ZXS=6.0 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
+          <t>ZXS=6.0 | Prefer=周一(6-7节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>新正龙(xkp01050039): 第1教学周已占6节; 第2教学周已占18节</t>
+          <t>新黎君(xkp01050034): 第1教学周已占2节; 第2教学周已占2节</t>
         </is>
       </c>
       <c r="N189" t="inlineStr"/>
@@ -14593,7 +14593,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>150130680.003</t>
+          <t>150130680.005</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14603,12 +14603,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
+          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=5.5</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=11.0</t>
+          <t>课程行校区=南校区 | 课容量=10.0</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -14628,7 +14628,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>ZXS=6.0 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
+          <t>ZXS=5.5 | Prefer=周一(6-7节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -14653,7 +14653,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>新海兵(xkp01050014): 第1教学周已占8节; 第2教学周已占8节</t>
+          <t>新孝志(xkp01050019): 第1教学周已占8节; 第2教学周已占14节 | 新娟(xkp01050085): 第1教学周已占8节; 第2教学周已占8节</t>
         </is>
       </c>
       <c r="N190" t="inlineStr"/>
@@ -14663,7 +14663,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>150130680.004</t>
+          <t>150130680.006</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14673,7 +14673,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
+          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=5.5</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -14698,7 +14698,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>ZXS=6.0 | Prefer=周一(6-7节) | unavail=周二(5-8节)</t>
+          <t>ZXS=5.5 | Prefer=周一(6-7节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -14723,7 +14723,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>新黎君(xkp01050034): 第1教学周已占2节; 第2教学周已占2节</t>
+          <t>新艳华(xkp01050031): 第1教学周已占4节; 第2教学周已占10节</t>
         </is>
       </c>
       <c r="N191" t="inlineStr"/>
@@ -14733,47 +14733,47 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>150130680.005</t>
+          <t>150130700.001</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>专项2</t>
+          <t>私人教练指导</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=5.5</t>
+          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=10.0</t>
+          <t>课程行校区=南校区 | 课容量=82.0</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>资源冲突或偏好过窄</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>① 偏好节次错位</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>ZXS=5.5 | Prefer=周一(6-7节) | unavail=周二(5-8节)</t>
+          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -14783,67 +14783,75 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1195（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新华伟(xkp01050027): 第1教学周已占2节; 第2教学周已占8节 | 新燕(xkp01050051): 第1教学周已占6节; 第2教学周已占6节 | 新燚(xkp01050067): 第1教学周已占4节; 第2教学周已占4节 | 新新海(xkp01050035): 第1教学周已占12节; 第2教学周已占12节</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>新孝志(xkp01050019): 第1教学周已占8节; 第2教学周已占14节 | 新娟(xkp01050085): 第1教学周已占8节; 第2教学周已占8节</t>
-        </is>
-      </c>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
+          <t>新华伟(xkp01050027): 第1教学周已占2节; 第2教学周已占8节 | 新燕(xkp01050051): 第1教学周已占6节; 第2教学周已占6节 | 新燚(xkp01050067): 第1教学周已占4节; 第2教学周已占4节 | 新新海(xkp01050035): 第1教学周已占12节; 第2教学周已占12节</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>偏好窗口外</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>偏好窗口外×1195</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>150130680.006</t>
+          <t>150130880.001</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>专项2</t>
+          <t>健身俱乐部经营与管理</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=5.5</t>
+          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周一全天；周二全天；周五全天 | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=3段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=10.0</t>
+          <t>课程行校区=南校区 | 课容量=82.0</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>资源冲突或偏好过窄</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>① 偏好节次错位</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>ZXS=5.5 | Prefer=周一(6-7节) | unavail=周二(5-8节)</t>
+          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -14853,32 +14861,40 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1195（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新永新(xkp01050075): 第1教学周已占6节; 第2教学周已占6节</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>新艳华(xkp01050031): 第1教学周已占4节; 第2教学周已占10节</t>
-        </is>
-      </c>
-      <c r="N193" t="inlineStr"/>
-      <c r="O193" t="inlineStr"/>
+          <t>新永新(xkp01050075): 第1教学周已占6节; 第2教学周已占6节</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>偏好窗口外</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>偏好窗口外×1195</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>150130700.001</t>
+          <t>150140220.001</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>私人教练指导</t>
+          <t>民间武术套路2</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -14888,7 +14904,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=82.0</t>
+          <t>课程行校区=南校区 | 课容量=41.0</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -14923,7 +14939,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1195（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新华伟(xkp01050027): 第1教学周已占2节; 第2教学周已占8节 | 新燕(xkp01050051): 第1教学周已占6节; 第2教学周已占6节 | 新燚(xkp01050067): 第1教学周已占4节; 第2教学周已占4节 | 新新海(xkp01050035): 第1教学周已占12节; 第2教学周已占12节</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1810（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14931,11 +14947,7 @@
           <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
         </is>
       </c>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>新华伟(xkp01050027): 第1教学周已占2节; 第2教学周已占8节 | 新燕(xkp01050051): 第1教学周已占6节; 第2教学周已占6节 | 新燚(xkp01050067): 第1教学周已占4节; 第2教学周已占4节 | 新新海(xkp01050035): 第1教学周已占12节; 第2教学周已占12节</t>
-        </is>
-      </c>
+      <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr">
         <is>
           <t>偏好窗口外</t>
@@ -14943,7 +14955,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>偏好窗口外×1195</t>
+          <t>偏好窗口外×1810</t>
         </is>
       </c>
       <c r="P194" t="inlineStr"/>
@@ -14951,22 +14963,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>150130880.001</t>
+          <t>150140470.002</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>健身俱乐部经营与管理</t>
+          <t>武术竞赛与训练2</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周一全天；周二全天；周五全天 | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=3段 | ZXS=2.0</t>
+          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=82.0</t>
+          <t>课程行校区=南校区 | 课容量=14.0</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -15001,7 +15013,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1195（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新永新(xkp01050075): 第1教学周已占6节; 第2教学周已占6节</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1980（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -15011,7 +15023,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>新永新(xkp01050075): 第1教学周已占6节; 第2教学周已占6节</t>
+          <t>新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -15021,7 +15033,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>偏好窗口外×1195</t>
+          <t>偏好窗口外×1980</t>
         </is>
       </c>
       <c r="P195" t="inlineStr"/>
@@ -15029,12 +15041,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>150140220.001</t>
+          <t>150140470.003</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>民间武术套路2</t>
+          <t>武术竞赛与训练2</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -15044,7 +15056,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=41.0</t>
+          <t>课程行校区=南校区 | 课容量=14.0</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -15079,7 +15091,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1810（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1980（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -15087,7 +15099,11 @@
           <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
         </is>
       </c>
-      <c r="M196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
+        </is>
+      </c>
       <c r="N196" t="inlineStr">
         <is>
           <t>偏好窗口外</t>
@@ -15095,7 +15111,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>偏好窗口外×1810</t>
+          <t>偏好窗口外×1980</t>
         </is>
       </c>
       <c r="P196" t="inlineStr"/>
@@ -15103,7 +15119,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>150140470.002</t>
+          <t>150140470.004</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15113,12 +15129,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=1.9999999</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=14.0</t>
+          <t>课程行校区=南校区 | 课容量=13.0</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -15153,7 +15169,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1980（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1980（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -15163,7 +15179,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
+          <t>新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -15181,12 +15197,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>150140470.003</t>
+          <t>150140490.002</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>武术竞赛与训练2</t>
+          <t>武术竞赛与训练4</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -15196,7 +15212,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=14.0</t>
+          <t>课程行校区=南校区 | 课容量=10.0</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -15231,7 +15247,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1980（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1985（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -15241,7 +15257,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
+          <t>新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -15251,7 +15267,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>偏好窗口外×1980</t>
+          <t>偏好窗口外×1985</t>
         </is>
       </c>
       <c r="P198" t="inlineStr"/>
@@ -15259,22 +15275,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>150140470.004</t>
+          <t>150140490.003</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>武术竞赛与训练2</t>
+          <t>武术竞赛与训练4</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=1.9999999</t>
+          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=13.0</t>
+          <t>课程行校区=南校区 | 课容量=10.0</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -15309,7 +15325,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1980（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1985（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -15319,7 +15335,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
+          <t>新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -15329,7 +15345,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>偏好窗口外×1980</t>
+          <t>偏好窗口外×1985</t>
         </is>
       </c>
       <c r="P199" t="inlineStr"/>
@@ -15337,7 +15353,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>150140490.002</t>
+          <t>150140490.004</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15387,7 +15403,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1985（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1985（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -15397,7 +15413,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
+          <t>新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15415,12 +15431,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>150140490.003</t>
+          <t>150140570.001</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>武术竞赛与训练4</t>
+          <t>散打2</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -15430,7 +15446,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=10.0</t>
+          <t>课程行校区=南校区 | 课容量=21.0</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -15465,7 +15481,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1985（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1965（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新新豪(xkp01050087): 第1教学周已占6节; 第2教学周已占6节</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -15475,7 +15491,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
+          <t>新新豪(xkp01050087): 第1教学周已占6节; 第2教学周已占6节</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -15485,7 +15501,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>偏好窗口外×1985</t>
+          <t>偏好窗口外×1965</t>
         </is>
       </c>
       <c r="P201" t="inlineStr"/>
@@ -15493,47 +15509,47 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>150140490.004</t>
+          <t>150140670.002</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>武术竞赛与训练4</t>
+          <t>专项3</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=周二（1-2节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=4.0</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=10.0</t>
+          <t>课程行校区=南校区 | 课容量=14.0 | 教室类型名称=体育类专用</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>资源冲突或偏好过窄</t>
+          <t>时间偏好与周学时</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>① 偏好节次错位</t>
+          <t>⓪ 日模式生成</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
+          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
+          <t>ZXS=4.0 | Prefer=周二(1-2节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
+          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -15543,75 +15559,67 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1985（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
+          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
+          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
-        </is>
-      </c>
-      <c r="N202" t="inlineStr">
-        <is>
-          <t>偏好窗口外</t>
-        </is>
-      </c>
-      <c r="O202" t="inlineStr">
-        <is>
-          <t>偏好窗口外×1985</t>
-        </is>
-      </c>
+          <t>新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>150140570.001</t>
+          <t>150140670.003</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>散打2</t>
+          <t>专项3</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=周二（1-2节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=4.0</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=21.0</t>
+          <t>课程行校区=南校区 | 课容量=15.0 | 教室类型名称=体育类专用</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>资源冲突或偏好过窄</t>
+          <t>时间偏好与周学时</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>① 偏好节次错位</t>
+          <t>⓪ 日模式生成</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
+          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
+          <t>ZXS=4.0 | Prefer=周二(1-2节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
+          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -15621,35 +15629,27 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1965（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新新豪(xkp01050087): 第1教学周已占6节; 第2教学周已占6节</t>
+          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
+          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>新新豪(xkp01050087): 第1教学周已占6节; 第2教学周已占6节</t>
-        </is>
-      </c>
-      <c r="N203" t="inlineStr">
-        <is>
-          <t>偏好窗口外</t>
-        </is>
-      </c>
-      <c r="O203" t="inlineStr">
-        <is>
-          <t>偏好窗口外×1965</t>
-        </is>
-      </c>
+          <t>新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
       <c r="P203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>150140670.002</t>
+          <t>150140670.004</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15659,7 +15659,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Prefer_Time=周二（1-2节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=4.0</t>
+          <t>Prefer_Time=周二（1-2节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=3.9999998</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -15684,7 +15684,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>ZXS=4.0 | Prefer=周二(1-2节) | unavail=周二(5-8节)</t>
+          <t>ZXS=3.9999998 | Prefer=周二(1-2节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -15709,7 +15709,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
+          <t>新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
         </is>
       </c>
       <c r="N204" t="inlineStr"/>
@@ -15719,12 +15719,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>150140670.003</t>
+          <t>150140760.002</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>专项3</t>
+          <t>专项5</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -15734,7 +15734,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=15.0 | 教室类型名称=体育类专用</t>
+          <t>课程行校区=南校区 | 课容量=14.0</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -15779,7 +15779,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
+          <t>新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
         </is>
       </c>
       <c r="N205" t="inlineStr"/>
@@ -15789,22 +15789,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>150140670.004</t>
+          <t>150140760.003</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>专项3</t>
+          <t>专项5</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Prefer_Time=周二（1-2节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=3.9999998</t>
+          <t>Prefer_Time=周二（1-2节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=4.0</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=14.0 | 教室类型名称=体育类专用</t>
+          <t>课程行校区=南校区 | 课容量=13.0</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -15824,7 +15824,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>ZXS=3.9999998 | Prefer=周二(1-2节) | unavail=周二(5-8节)</t>
+          <t>ZXS=4.0 | Prefer=周二(1-2节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -15849,7 +15849,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
+          <t>新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
         </is>
       </c>
       <c r="N206" t="inlineStr"/>
@@ -15859,7 +15859,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>150140760.002</t>
+          <t>150140760.004</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15874,7 +15874,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=14.0</t>
+          <t>课程行校区=南校区 | 课容量=13.0</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -15919,7 +15919,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
+          <t>新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
         </is>
       </c>
       <c r="N207" t="inlineStr"/>
@@ -15929,12 +15929,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>150140760.003</t>
+          <t>151130120.001</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>专项5</t>
+          <t>乒乓球</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -15944,7 +15944,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=13.0</t>
+          <t>课程行校区=南校区 | 课容量=41.0</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -15987,11 +15987,7 @@
           <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
         </is>
       </c>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
-        </is>
-      </c>
+      <c r="M208" t="inlineStr"/>
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="inlineStr"/>
@@ -15999,47 +15995,47 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>150140760.004</t>
+          <t>160060320.047</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>专项5</t>
+          <t>声乐4</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Prefer_Time=周二（1-2节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=4.0</t>
+          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=13.0</t>
+          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>资源冲突或偏好过窄</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>③ 教师时段饱和</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>ZXS=4.0 | Prefer=周二(1-2节) | unavail=周二(5-8节)</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -16049,67 +16045,75 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
-        </is>
-      </c>
-      <c r="N209" t="inlineStr"/>
-      <c r="O209" t="inlineStr"/>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>偏好窗口外</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
+        </is>
+      </c>
       <c r="P209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>151130120.001</t>
+          <t>160060320.048</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>乒乓球</t>
+          <t>声乐4</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Prefer_Time=周二（1-2节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=4.0</t>
+          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=41.0</t>
+          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>资源冲突或偏好过窄</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>③ 教师时段饱和</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>ZXS=4.0 | Prefer=周二(1-2节) | unavail=周二(5-8节)</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -16119,23 +16123,35 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
-        </is>
-      </c>
-      <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
-      <c r="O210" t="inlineStr"/>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>偏好窗口外</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>160060320.047</t>
+          <t>160060320.049</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16213,7 +16229,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>160060320.048</t>
+          <t>160060320.050</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16291,7 +16307,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>160060320.049</t>
+          <t>160060320.051</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16369,7 +16385,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>160060320.050</t>
+          <t>160060320.052</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16447,12 +16463,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>160060320.051</t>
+          <t>160060340.047</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>声乐4</t>
+          <t>声乐6</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -16525,12 +16541,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>160060320.052</t>
+          <t>160060340.048</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>声乐4</t>
+          <t>声乐6</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -16603,7 +16619,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>160060340.047</t>
+          <t>160060340.049</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16681,7 +16697,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>160060340.048</t>
+          <t>160060340.050</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16759,7 +16775,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>160060340.049</t>
+          <t>160060340.051</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -16837,17 +16853,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>160060340.050</t>
+          <t>160060360.040</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>声乐6</t>
+          <t>声乐8</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
+          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -16887,7 +16903,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=405（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -16907,7 +16923,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
+          <t>偏好窗口外×405；教室占用×191；教师占用×79</t>
         </is>
       </c>
       <c r="P220" t="inlineStr"/>
@@ -16915,17 +16931,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>160060340.051</t>
+          <t>160060360.041</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>声乐6</t>
+          <t>声乐8</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
+          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -16965,7 +16981,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=405（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -16985,7 +17001,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
+          <t>偏好窗口外×405；教室占用×191；教师占用×79</t>
         </is>
       </c>
       <c r="P221" t="inlineStr"/>
@@ -16993,7 +17009,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>160060360.040</t>
+          <t>160060360.042</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17043,7 +17059,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=405（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×190；教师占用×80。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=405（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -17063,7 +17079,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>偏好窗口外×405；教室占用×190；教师占用×80</t>
+          <t>偏好窗口外×405；教室占用×191；教师占用×79</t>
         </is>
       </c>
       <c r="P222" t="inlineStr"/>
@@ -17071,12 +17087,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>160060360.041</t>
+          <t>160060430.001</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>声乐8</t>
+          <t>声乐艺术史及作品欣赏2</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -17086,7 +17102,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
+          <t>课程行校区=南校区 | 课容量=100.0 | 教室类型名称=艺术类专用</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -17096,44 +17112,44 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>③ 教师时段饱和</t>
+          <t>② 教室时段占用</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
+          <t>教室时段被占满(已通过时间窗口)</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
+          <t>ZXS=2.0 | Prefer=周三(5-8节)、周四(5-8节)、周五(5-8节)</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>扩候选教室 / 错峰该教室既有占用</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>一级</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=18（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=12（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×12。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
           <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>一级</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=405（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×190；教师占用×80。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="L223" t="inlineStr">
-        <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
-        </is>
-      </c>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
       <c r="N223" t="inlineStr">
         <is>
           <t>偏好窗口外</t>
@@ -17141,7 +17157,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>偏好窗口外×405；教室占用×190；教师占用×80</t>
+          <t>偏好窗口外×18；教室占用×12</t>
         </is>
       </c>
       <c r="P223" t="inlineStr"/>
@@ -17149,17 +17165,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>160060360.042</t>
+          <t>16502002.041</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>声乐8</t>
+          <t>声乐2</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=2.0</t>
+          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -17199,7 +17215,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=405（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×190；教师占用×80。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -17219,7 +17235,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>偏好窗口外×405；教室占用×190；教师占用×80</t>
+          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
         </is>
       </c>
       <c r="P224" t="inlineStr"/>
@@ -17227,22 +17243,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>160060430.001</t>
+          <t>16502002.042</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>声乐艺术史及作品欣赏2</t>
+          <t>声乐2</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=2.0</t>
+          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=100.0 | 教室类型名称=艺术类专用</t>
+          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -17252,22 +17268,22 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>② 教室时段占用</t>
+          <t>③ 教师时段饱和</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>教室时段被占满(已通过时间窗口)</t>
+          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>ZXS=2.0 | Prefer=周三(5-8节)、周四(5-8节)、周五(5-8节)</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>扩候选教室 / 错峰该教室既有占用</t>
+          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -17277,7 +17293,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=18（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=12（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×12。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -17297,7 +17313,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>偏好窗口外×18；教室占用×12</t>
+          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
         </is>
       </c>
       <c r="P225" t="inlineStr"/>
@@ -17305,7 +17321,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>16502002.041</t>
+          <t>16502002.043</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17383,7 +17399,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>16502002.042</t>
+          <t>16502002.044</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17461,178 +17477,154 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>16502002.043</t>
+          <t>271010080.001</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>声乐2</t>
+          <t>Java EE开发技术</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
+          <t>Prefer_Time=周三全天；周四全天 | unavailable_Time=周一全天；周二全天；周五全天 | 解析后 preferred_groups=0组 | preferred_options=2条 | 禁止时段解析块=3段 | ZXS=3.5</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
+          <t>课程行校区=北校区 | 课容量=204.0</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>资源冲突或偏好过窄</t>
+          <t>教室静态不可行</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>③ 教师时段饱和</t>
+          <t>⓪ 教室预筛</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
+          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+          <t>ZXS=3.5 | Prefer=周三全天;周四全天</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
+          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>一级</t>
+          <t>二级</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
-        </is>
-      </c>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="N228" t="inlineStr">
-        <is>
-          <t>偏好窗口外</t>
-        </is>
-      </c>
-      <c r="O228" t="inlineStr">
-        <is>
-          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
-        </is>
-      </c>
+          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
+      <c r="O228" t="inlineStr"/>
       <c r="P228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>16502002.044</t>
+          <t>271010091.002</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>声乐2</t>
+          <t>移动开发技术</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
+          <t>课程行校区=北校区 | 课容量=204.0</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>资源冲突或偏好过窄</t>
+          <t>教室静态不可行</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>③ 教师时段饱和</t>
+          <t>⓪ 教室预筛</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
+          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+          <t>ZXS=4.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
+          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>一级</t>
+          <t>二级</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
-        </is>
-      </c>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="N229" t="inlineStr">
-        <is>
-          <t>偏好窗口外</t>
-        </is>
-      </c>
-      <c r="O229" t="inlineStr">
-        <is>
-          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
-        </is>
-      </c>
+          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr"/>
       <c r="P229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>271010080.001</t>
+          <t>271030050.001</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Java EE开发技术</t>
+          <t>网络编程提高</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Prefer_Time=周三全天；周四全天 | unavailable_Time=周一全天；周二全天；周五全天 | 解析后 preferred_groups=0组 | preferred_options=2条 | 禁止时段解析块=3段 | ZXS=3.5</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>课程行校区=北校区 | 课容量=204.0</t>
+          <t>课程行校区=北校区 | 课容量=247.0</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -17652,7 +17644,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>ZXS=3.5 | Prefer=周三全天;周四全天</t>
+          <t>ZXS=4.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -17680,138 +17672,6 @@
       <c r="O230" t="inlineStr"/>
       <c r="P230" t="inlineStr"/>
     </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>271010091.002</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>移动开发技术</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>课程行校区=北校区 | 课容量=204.0</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>教室静态不可行</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>⓪ 教室预筛</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>ZXS=4.0 | Prefer=无</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t>二级</t>
-        </is>
-      </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
-        </is>
-      </c>
-      <c r="L231" t="inlineStr">
-        <is>
-          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
-        </is>
-      </c>
-      <c r="M231" t="inlineStr"/>
-      <c r="N231" t="inlineStr"/>
-      <c r="O231" t="inlineStr"/>
-      <c r="P231" t="inlineStr"/>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>271030050.001</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>网络编程提高</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>课程行校区=北校区 | 课容量=247.0</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>教室静态不可行</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>⓪ 教室预筛</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
-        </is>
-      </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>ZXS=4.0 | Prefer=无</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
-        </is>
-      </c>
-      <c r="J232" t="inlineStr">
-        <is>
-          <t>二级</t>
-        </is>
-      </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
-        </is>
-      </c>
-      <c r="L232" t="inlineStr">
-        <is>
-          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
-        </is>
-      </c>
-      <c r="M232" t="inlineStr"/>
-      <c r="N232" t="inlineStr"/>
-      <c r="O232" t="inlineStr"/>
-      <c r="P232" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/排课结果/失败课程归因与建议.xlsx
+++ b/排课结果/失败课程归因与建议.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O177"/>
+  <dimension ref="A1:O163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -700,7 +700,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=295（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新永新(xkp01050075): 第1教学周已占8节; 第2教学周已占8节</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=295（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新永新(xkp01050075): 第1教学周已占8节; 第2教学周已占14节</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>新永新(xkp01050075): 第1教学周已占8节; 第2教学周已占8节</t>
+          <t>新永新(xkp01050075): 第1教学周已占8节; 第2教学周已占14节</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=295（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新永新(xkp01050075): 第1教学周已占8节; 第2教学周已占8节</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=295（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新永新(xkp01050075): 第1教学周已占8节; 第2教学周已占14节</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>新永新(xkp01050075): 第1教学周已占8节; 第2教学周已占8节</t>
+          <t>新永新(xkp01050075): 第1教学周已占8节; 第2教学周已占14节</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=295（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新永新(xkp01050075): 第1教学周已占8节; 第2教学周已占8节</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=295（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新永新(xkp01050075): 第1教学周已占8节; 第2教学周已占14节</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>新永新(xkp01050075): 第1教学周已占8节; 第2教学周已占8节</t>
+          <t>新永新(xkp01050075): 第1教学周已占8节; 第2教学周已占14节</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -6567,136 +6567,132 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>110000460.006</t>
+          <t>091000021.001</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>高等数学b-2</t>
+          <t>网页设计基础</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Prefer_Time=周六全天；周日全天 | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=2条 | 禁止时段解析块=1段 | ZXS=6.0</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=150.0 | 教室类型名称=固定桌椅多媒体</t>
+          <t>课程行校区=南校区 | 课容量=819.0</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>教室静态不可行</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>⓪ 教室预筛</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>ZXS=6.0 | Prefer=周六全天;周日全天 | unavail=周二(5-8节)</t>
+          <t>ZXS=2.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>一级</t>
+          <t>二级</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>新新霞(xkp01230481): 第3教学周已占4节; 第4教学周已占4节</t>
-        </is>
-      </c>
+          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>110000480.001</t>
+          <t>121000111.004</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>高等数学c-2</t>
+          <t>社会主义发展史</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Prefer_Time=周六全天；周日全天 | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=2条 | 禁止时段解析块=1段 | ZXS=6.0</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=190.0 | 教室类型名称=固定桌椅多媒体</t>
+          <t>课程行校区=北校区 | 课容量=247.0 | 教室类型名称=固定桌椅多媒体</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>教室静态不可行</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>⓪ 教室预筛</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>ZXS=6.0 | Prefer=周六全天;周日全天 | unavail=周二(5-8节)</t>
+          <t>ZXS=2.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>一级</t>
+          <t>二级</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>新岩(xkp01040094): 第3教学周已占6节; 第4教学周已占6节</t>
+          <t>新莉(xkp01010049): 第1教学周已占18节; 第2教学周已占18节</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -6705,132 +6701,136 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>110000480.002</t>
+          <t>121000121.001</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>高等数学c-2</t>
+          <t>大学生职业软技能实训课程</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Prefer_Time=周六全天；周日全天 | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=2条 | 禁止时段解析块=1段 | ZXS=6.0</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=190.0 | 教室类型名称=固定桌椅多媒体</t>
+          <t>课程行校区=南校区 | 课容量=127.0 | 教室类型名称=活动桌椅多媒体</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>教室静态不可行</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>⓪ 教室预筛</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>ZXS=6.0 | Prefer=周六全天;周日全天 | unavail=周二(5-8节)</t>
+          <t>ZXS=4.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>一级</t>
+          <t>二级</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr"/>
+          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>新新印(xkp01010037): 第7教学周已占16节; 第8教学周已占16节</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>110000670.002</t>
+          <t>14200002.006</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>高等数学a-2</t>
+          <t>大学外语2</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Prefer_Time=周六全天；周日全天 | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=2条 | 禁止时段解析块=1段 | ZXS=6.0</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>课程行校区=北校区 | 课容量=180.0 | 教室类型名称=固定桌椅多媒体</t>
+          <t>课程行校区=南校区 | 课容量=612.0</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>教室静态不可行</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>⓪ 教室预筛</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>ZXS=6.0 | Prefer=周六全天;周日全天 | unavail=周二(5-8节)</t>
+          <t>ZXS=2.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>一级</t>
+          <t>二级</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>新世佼(xkp01040064): 第3教学周已占6节; 第4教学周已占6节</t>
+          <t>新伟(xkp01020119): 第1教学周已占8节; 第2教学周已占8节</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -6839,12 +6839,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>091000021.001</t>
+          <t>14200002.009</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>网页设计基础</t>
+          <t>大学外语2</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=819.0</t>
+          <t>课程行校区=南校区 | 课容量=612.0</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -6897,19 +6897,23 @@
           <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>新大维(xkp01020102): 第1教学周已占10节; 第2教学周已占10节</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>121000111.004</t>
+          <t>14200002.075</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>社会主义发展史</t>
+          <t>大学外语2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6919,7 +6923,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>课程行校区=北校区 | 课容量=247.0 | 教室类型名称=固定桌椅多媒体</t>
+          <t>课程行校区=南校区 | 课容量=914.0</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -6964,7 +6968,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>新莉(xkp01010049): 第1教学周已占18节; 第2教学周已占18节</t>
+          <t>新静晓(xkp01230768): 第1教学周已占8节; 第2教学周已占8节</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -6973,22 +6977,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>121000121.001</t>
+          <t>14200002.076</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>大学生职业软技能实训课程</t>
+          <t>大学外语2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=127.0 | 教室类型名称=活动桌椅多媒体</t>
+          <t>课程行校区=南校区 | 课容量=914.0</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7008,7 +7012,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>ZXS=4.0 | Prefer=无</t>
+          <t>ZXS=2.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7033,7 +7037,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>新新印(xkp01010037): 第7教学周已占16节; 第8教学周已占16节</t>
+          <t>新阳晓(xkp01020064): 第1教学周已占8节; 第2教学周已占8节</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -7042,67 +7046,67 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>130000510.002</t>
+          <t>14200002.077</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>大学外语2</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Prefer_Time=周六全天；周日全天 | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=2条 | 禁止时段解析块=1段 | ZXS=7.0</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=165.0 | 教室类型名称=固定桌椅多媒体</t>
+          <t>课程行校区=南校区 | 课容量=914.0</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>教室静态不可行</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>⓪ 教室预筛</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>ZXS=7.0 | Prefer=周六全天;周日全天 | unavail=周二(5-8节)</t>
+          <t>ZXS=2.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>一级</t>
+          <t>二级</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>新卫彬(xkp01030027): 第2教学周已占4节; 第3教学周已占4节</t>
+          <t>新玉双(xkp01020138): 第1教学周已占8节; 第2教学周已占8节</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -7111,67 +7115,67 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>130000510.004</t>
+          <t>14200002.078</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>大学外语2</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Prefer_Time=周六全天；周日全天 | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=2条 | 禁止时段解析块=1段 | ZXS=7.0</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=165.0 | 教室类型名称=固定桌椅多媒体</t>
+          <t>课程行校区=南校区 | 课容量=914.0</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>教室静态不可行</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>⓪ 教室预筛</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>ZXS=7.0 | Prefer=周六全天;周日全天 | unavail=周二(5-8节)</t>
+          <t>ZXS=2.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>一级</t>
+          <t>二级</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>新振深(xkp01030005): 第2教学周已占8节; 第3教学周已占8节</t>
+          <t>新会霞(xkp01020043): 第1教学周已占8节; 第2教学周已占8节</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -7180,67 +7184,67 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>130000510.005</t>
+          <t>14200002.080</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>大学外语2</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Prefer_Time=周六全天；周日全天 | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=2条 | 禁止时段解析块=1段 | ZXS=7.0</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=165.0 | 教室类型名称=固定桌椅多媒体</t>
+          <t>课程行校区=南校区 | 课容量=914.0</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>教室静态不可行</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>⓪ 教室预筛</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>ZXS=7.0 | Prefer=周六全天;周日全天 | unavail=周二(5-8节)</t>
+          <t>ZXS=2.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>一级</t>
+          <t>二级</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>新宝基(xkp01030037): 第2教学周已占8节; 第3教学周已占8节</t>
+          <t>新佑娟(xkp01020056): 第1教学周已占8节; 第2教学周已占8节</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -7249,67 +7253,67 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>130000510.006</t>
+          <t>171000121.032</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>影视鉴赏</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Prefer_Time=周六全天；周日全天 | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=2条 | 禁止时段解析块=1段 | ZXS=7.0</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=165.0 | 教室类型名称=固定桌椅多媒体</t>
+          <t>课程行校区=南校区 | 课容量=369.0</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>教室静态不可行</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>⓪ 教室预筛</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>ZXS=7.0 | Prefer=周六全天;周日全天 | unavail=周二(5-8节)</t>
+          <t>ZXS=2.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>一级</t>
+          <t>二级</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>新玉新(xkp01170071): 第2教学周已占8节; 第3教学周已占8节</t>
+          <t>新静(xkp01020127): 第1教学周已占2节; 第2教学周已占2节</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -7318,67 +7322,67 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>130000510.007</t>
+          <t>261000011.001</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>生活中的健康管理</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Prefer_Time=周六全天；周日全天 | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=2条 | 禁止时段解析块=1段 | ZXS=7.0</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=165.0 | 教室类型名称=固定桌椅多媒体</t>
+          <t>课程行校区=北校区 | 课容量=255.0</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>教室静态不可行</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>⓪ 教室预筛</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>ZXS=7.0 | Prefer=周六全天;周日全天 | unavail=周二(5-8节)</t>
+          <t>ZXS=2.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>一级</t>
+          <t>二级</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>新保立(xkp01030033): 第2教学周已占8节; 第3教学周已占8节</t>
+          <t>新攀(xkp01220224): 第5教学周已占4节; 第6教学周已占4节 | 新荣荣(xkp01220255): 第5教学周已占2节; 第6教学周已占2节 | 新蕾(xkp01220241): 第5教学周已占4节; 第6教学周已占4节 | 新新岭(xkp01220229): 第5教学周已占4节</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -7387,67 +7391,67 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>130000510.008</t>
+          <t>26100003M.006</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>“救”在你身边</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Prefer_Time=周六全天；周日全天 | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=2条 | 禁止时段解析块=1段 | ZXS=7.0</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=165.0 | 教室类型名称=固定桌椅多媒体</t>
+          <t>课程行校区=北校区 | 课容量=197.0</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>教室静态不可行</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>⓪ 教室预筛</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>ZXS=7.0 | Prefer=周六全天;周日全天 | unavail=周二(5-8节)</t>
+          <t>ZXS=2.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>一级</t>
+          <t>二级</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>新岩松(xkp01030050): 第2教学周已占8节; 第3教学周已占8节</t>
+          <t>新新(xkp01220242): 第8教学周已占15节; 第9教学周已占15节</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -7456,67 +7460,67 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>130000510.009</t>
+          <t>61660003.001</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>音乐美学</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Prefer_Time=周六全天；周日全天 | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=2条 | 禁止时段解析块=1段 | ZXS=7.0</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=1.9999999</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=165.0 | 教室类型名称=固定桌椅多媒体</t>
+          <t>课程行校区=南校区 | 课容量=125.0 | 教室类型名称=活动桌椅多媒体</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>教室静态不可行</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>⓪ 教室预筛</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>ZXS=7.0 | Prefer=周六全天;周日全天 | unavail=周二(5-8节)</t>
+          <t>ZXS=1.9999999 | Prefer=无</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>一级</t>
+          <t>二级</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>新舰(xkp01030098): 第2教学周已占8节; 第3教学周已占8节</t>
+          <t>新洁(xkp01230598): 第2教学周已占11节; 第3教学周已占11节</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -7525,67 +7529,67 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>130000510.010</t>
+          <t>61660003.002</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>音乐美学</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Prefer_Time=周六全天；周日全天 | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=2条 | 禁止时段解析块=1段 | ZXS=7.0</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=180.0 | 教室类型名称=固定桌椅多媒体</t>
+          <t>课程行校区=北校区 | 课容量=60.0 | 教室类型名称=活动桌椅教室</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>教室静态不可行</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>⓪ 教室预筛</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>ZXS=7.0 | Prefer=周六全天;周日全天 | unavail=周二(5-8节)</t>
+          <t>ZXS=2.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>一级</t>
+          <t>二级</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>新新(xkp01030018): 第2教学周已占8节; 第3教学周已占8节</t>
+          <t>新洁(xkp01230598): 第2教学周已占11节; 第3教学周已占11节</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -7594,12 +7598,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>14200002.006</t>
+          <t>61660004.002</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>大学外语2</t>
+          <t>音乐鉴赏</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7609,7 +7613,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=612.0</t>
+          <t>课程行校区=北校区 | 课容量=60.0 | 教室类型名称=活动桌椅多媒体</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -7654,7 +7658,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>新伟(xkp01020119): 第1教学周已占8节; 第2教学周已占8节</t>
+          <t>新萌(xkp01231226): 第2教学周已占4节; 第3教学周已占4节</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -7663,12 +7667,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>14200002.009</t>
+          <t>61660008.001</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>大学外语2</t>
+          <t>世界音乐与多元文化</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7678,7 +7682,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=612.0</t>
+          <t>课程行校区=南校区 | 课容量=125.0 | 教室类型名称=活动桌椅多媒体</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -7723,7 +7727,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>新大维(xkp01020102): 第1教学周已占10节; 第2教学周已占10节</t>
+          <t>新颖(xkp01200657): 第2教学周已占2节; 第3教学周已占2节</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -7732,12 +7736,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>14200002.075</t>
+          <t>61660009.001</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>大学外语2</t>
+          <t>怀川弦歌：黄河文明的乐舞史诗</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7747,7 +7751,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=914.0</t>
+          <t>课程行校区=南校区 | 课容量=60.0 | 教室类型名称=活动桌椅教室</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -7792,7 +7796,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>新静晓(xkp01230768): 第1教学周已占8节; 第2教学周已占8节</t>
+          <t>新庆花(xkp01010021): 第2教学周已占6节; 第3教学周已占6节</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -7801,12 +7805,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>14200002.076</t>
+          <t>61660010.002</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>大学外语2</t>
+          <t>舞蹈鉴赏</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7816,7 +7820,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=914.0</t>
+          <t>课程行校区=北校区 | 课容量=60.0 | 教室类型名称=活动桌椅多媒体</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -7861,7 +7865,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>新阳晓(xkp01020064): 第1教学周已占8节; 第2教学周已占8节</t>
+          <t>新吉宁(xkp01230973): 第2教学周已占14节; 第3教学周已占14节</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -7870,12 +7874,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>14200002.077</t>
+          <t>61660011.001</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>大学外语2</t>
+          <t>戏剧鉴赏</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7885,7 +7889,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=914.0</t>
+          <t>课程行校区=南校区 | 课容量=60.0 | 教室类型名称=活动桌椅教室</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -7930,7 +7934,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>新玉双(xkp01020138): 第1教学周已占8节; 第2教学周已占8节</t>
+          <t>新茜(xkp01200000): 第2教学周已占4节; 第3教学周已占4节</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -7939,12 +7943,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>14200002.078</t>
+          <t>61660011.002</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>大学外语2</t>
+          <t>戏剧鉴赏</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7954,7 +7958,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=914.0</t>
+          <t>课程行校区=北校区 | 课容量=60.0 | 教室类型名称=活动桌椅多媒体</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -7999,7 +8003,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>新会霞(xkp01020043): 第1教学周已占8节; 第2教学周已占8节</t>
+          <t>新茜(xkp01200000): 第2教学周已占4节; 第3教学周已占4节</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -8008,22 +8012,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>14200002.080</t>
+          <t>61660012.002</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>大学外语2</t>
+          <t>音乐的美感特征：流行中的音乐</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=914.0</t>
+          <t>课程行校区=北校区 | 课容量=60.0 | 教室类型名称=活动桌椅多媒体</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -8043,7 +8047,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>ZXS=2.0 | Prefer=无</t>
+          <t>ZXS=2.0 | Prefer=周三(5-8节)、周四(5-8节)、周五(5-8节)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -8068,7 +8072,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>新佑娟(xkp01020056): 第1教学周已占8节; 第2教学周已占8节</t>
+          <t>新旋(xkp01200395): 第2教学周已占11节; 第3教学周已占11节</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -8077,67 +8081,67 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>15ALT016.003</t>
+          <t>61660012.004</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>队田径业余队</t>
+          <t>音乐的美感特征：流行中的音乐</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Prefer_Time=周三全天；周四全天 | unavailable_Time=周一全天；周二全天；周五全天 | 解析后 preferred_groups=0组 | preferred_options=2条 | 禁止时段解析块=3段 | ZXS=6.0</t>
+          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=0.0</t>
+          <t>课程行校区=北校区 | 课容量=60.0 | 教室类型名称=活动桌椅多媒体</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>教室静态不可行</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>⓪ 教室预筛</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>ZXS=6.0 | Prefer=周三全天;周四全天 | unavail=周一全天;周二全天;周五全天</t>
+          <t>ZXS=2.0 | Prefer=周三(5-8节)、周四(5-8节)、周五(5-8节)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>一级</t>
+          <t>二级</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>新永新(xkp01050075): 第2教学周已占8节; 第3教学周已占8节</t>
+          <t>新旋(xkp01200395): 第2教学周已占11节; 第3教学周已占11节</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -8146,12 +8150,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>171000121.032</t>
+          <t>61921003.001</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>影视鉴赏</t>
+          <t>职场礼仪与高情商沟通</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -8161,7 +8165,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=369.0</t>
+          <t>课程行校区=南校区 | 课容量=280.0 | 教室类型名称=固定桌椅多媒体</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -8206,7 +8210,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>新静(xkp01020127): 第1教学周已占2节; 第2教学周已占2节</t>
+          <t>新晓冰(xkp01090150): 第13教学周已占4节; 第14教学周已占4节</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -8215,12 +8219,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>261000011.001</t>
+          <t>62221001.002</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>生活中的健康管理</t>
+          <t>侦探之旅：从柯南道尔到AI司鉴</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -8230,7 +8234,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>课程行校区=北校区 | 课容量=255.0</t>
+          <t>课程行校区=北校区 | 课容量=210.0</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -8275,7 +8279,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>新攀(xkp01220224): 第5教学周已占4节; 第6教学周已占4节 | 新荣荣(xkp01220255): 第5教学周已占2节; 第6教学周已占2节 | 新蕾(xkp01220241): 第5教学周已占4节; 第6教学周已占4节 | 新新岭(xkp01220229): 第5教学周已占4节</t>
+          <t>新蒙(xkp01231016): 第9教学周已占2节; 第10教学周已占2节</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -8284,22 +8288,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>26100003M.006</t>
+          <t>081010790.001</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>“救”在你身边</t>
+          <t>高电压技术</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=5.5</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>课程行校区=北校区 | 课容量=197.0</t>
+          <t>课程行校区=南校区 | 课容量=304.0 | 教室类型名称=固定桌椅多媒体</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -8319,7 +8323,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>ZXS=2.0 | Prefer=无</t>
+          <t>ZXS=5.5 | Prefer=无</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -8344,7 +8348,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>新新(xkp01220242): 第8教学周已占15节; 第9教学周已占15节</t>
+          <t>新来军(xkp01060067): 第6教学周已占6节; 第7教学周已占6节</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
@@ -8353,22 +8357,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>61660003.001</t>
+          <t>081010810.001</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>音乐美学</t>
+          <t>现代电气控制技术与PLC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=1.9999999</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=125.0 | 教室类型名称=活动桌椅多媒体</t>
+          <t>课程行校区=南校区 | 课容量=270.0 | 教室类型名称=固定桌椅多媒体</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -8388,7 +8392,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>ZXS=1.9999999 | Prefer=无</t>
+          <t>ZXS=4.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -8411,33 +8415,29 @@
           <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>新洁(xkp01230598): 第2教学周已占11节; 第3教学周已占11节</t>
-        </is>
-      </c>
+      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>61660003.002</t>
+          <t>090010740.002</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>音乐美学</t>
+          <t>大数据分析技术</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>课程行校区=北校区 | 课容量=60.0 | 教室类型名称=活动桌椅教室</t>
+          <t>课程行校区=北校区 | 课容量=204.0</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>ZXS=2.0 | Prefer=无</t>
+          <t>ZXS=4.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>新洁(xkp01230598): 第2教学周已占11节; 第3教学周已占11节</t>
+          <t>新朝生(xkp01070108): 第7教学周已占8节; 第8教学周已占8节</t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
@@ -8491,22 +8491,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>61660004.002</t>
+          <t>091010020.001</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>音乐鉴赏</t>
+          <t>算法分析与设计</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>课程行校区=北校区 | 课容量=60.0 | 教室类型名称=活动桌椅多媒体</t>
+          <t>课程行校区=北校区 | 课容量=245.0</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>ZXS=2.0 | Prefer=无</t>
+          <t>ZXS=4.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>新萌(xkp01231226): 第2教学周已占4节; 第3教学周已占4节</t>
+          <t>新东(xkp01079355): 第9教学周已占8节; 第10教学周已占8节</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -8560,22 +8560,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>61660008.001</t>
+          <t>091017031.001</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>世界音乐与多元文化</t>
+          <t>文献检索与科技论文写作</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=125.0 | 教室类型名称=活动桌椅多媒体</t>
+          <t>课程行校区=北校区 | 课容量=204.0</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>ZXS=2.0 | Prefer=无</t>
+          <t>ZXS=4.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>新颖(xkp01200657): 第2教学周已占2节; 第3教学周已占2节</t>
+          <t>新富凯(xkp01230450): 第13教学周已占8节; 第14教学周已占8节</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -8629,22 +8629,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>61660009.001</t>
+          <t>091058011.001</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>怀川弦歌：黄河文明的乐舞史诗</t>
+          <t>软件新技术讲座</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=60.0 | 教室类型名称=活动桌椅教室</t>
+          <t>课程行校区=北校区 | 课容量=204.0</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>ZXS=2.0 | Prefer=无</t>
+          <t>ZXS=4.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8687,147 +8687,151 @@
           <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>新庆花(xkp01010021): 第2教学周已占6节; 第3教学周已占6节</t>
-        </is>
-      </c>
+      <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>61660010.002</t>
+          <t>150010280.001</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>舞蹈鉴赏</t>
+          <t>运动处方理论与应用</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=周五（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=1.9999999</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>课程行校区=北校区 | 课容量=60.0 | 教室类型名称=活动桌椅多媒体</t>
+          <t>课程行校区=南校区 | 课容量=82.0</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>教室静态不可行</t>
+          <t>资源冲突或偏好过窄</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>⓪ 教室预筛</t>
+          <t>① 偏好节次错位</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
+          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>ZXS=2.0 | Prefer=无</t>
+          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
+          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>二级</t>
+          <t>一级</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1195（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新燚(xkp01050067): 第1教学周已占4节; 第2教学周已占4节</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>新吉宁(xkp01230973): 第2教学周已占14节; 第3教学周已占14节</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
+          <t>新燚(xkp01050067): 第1教学周已占4节; 第2教学周已占4节</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>偏好窗口外</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>偏好窗口外×1195</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>61660011.001</t>
+          <t>150130580.002</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>戏剧鉴赏</t>
+          <t>专项4</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=60.0 | 教室类型名称=活动桌椅教室</t>
+          <t>课程行校区=南校区 | 课容量=7.0</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>教室静态不可行</t>
+          <t>时间偏好与周学时</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>⓪ 教室预筛</t>
+          <t>⓪ 日模式生成</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
+          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>ZXS=2.0 | Prefer=无</t>
+          <t>ZXS=6.0 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
+          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>二级</t>
+          <t>一级</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
+          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
+          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>新茜(xkp01200000): 第2教学周已占4节; 第3教学周已占4节</t>
+          <t>新建营(xkp01050033): 第1教学周已占12节; 第2教学周已占18节</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -8836,67 +8840,67 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>61660011.002</t>
+          <t>150130580.003</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>戏剧鉴赏</t>
+          <t>专项4</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>课程行校区=北校区 | 课容量=60.0 | 教室类型名称=活动桌椅多媒体</t>
+          <t>课程行校区=南校区 | 课容量=14.0</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>教室静态不可行</t>
+          <t>时间偏好与周学时</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>⓪ 教室预筛</t>
+          <t>⓪ 日模式生成</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
+          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>ZXS=2.0 | Prefer=无</t>
+          <t>ZXS=6.0 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
+          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>二级</t>
+          <t>一级</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
+          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
+          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>新茜(xkp01200000): 第2教学周已占4节; 第3教学周已占4节</t>
+          <t>新毅新(xkp01050084): 第1教学周已占12节; 第2教学周已占12节</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -8905,67 +8909,67 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>61660012.002</t>
+          <t>150130580.004</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>音乐的美感特征：流行中的音乐</t>
+          <t>专项4</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=2.0</t>
+          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>课程行校区=北校区 | 课容量=60.0 | 教室类型名称=活动桌椅多媒体</t>
+          <t>课程行校区=南校区 | 课容量=14.0</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>教室静态不可行</t>
+          <t>时间偏好与周学时</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>⓪ 教室预筛</t>
+          <t>⓪ 日模式生成</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
+          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>ZXS=2.0 | Prefer=周三(5-8节)、周四(5-8节)、周五(5-8节)</t>
+          <t>ZXS=6.0 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
+          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>二级</t>
+          <t>一级</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
+          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
+          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>新旋(xkp01200395): 第2教学周已占11节; 第3教学周已占11节</t>
+          <t>新军勇(xkp01050009): 第1教学周已占10节; 第2教学周已占10节</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -8974,67 +8978,67 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>61660012.004</t>
+          <t>150130580.005</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>音乐的美感特征：流行中的音乐</t>
+          <t>专项4</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=2.0</t>
+          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>课程行校区=北校区 | 课容量=60.0 | 教室类型名称=活动桌椅多媒体</t>
+          <t>课程行校区=南校区 | 课容量=14.0</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>教室静态不可行</t>
+          <t>时间偏好与周学时</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>⓪ 教室预筛</t>
+          <t>⓪ 日模式生成</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
+          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>ZXS=2.0 | Prefer=周三(5-8节)、周四(5-8节)、周五(5-8节)</t>
+          <t>ZXS=6.0 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
+          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>二级</t>
+          <t>一级</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
+          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
+          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>新旋(xkp01200395): 第2教学周已占11节; 第3教学周已占11节</t>
+          <t>新希丹(xkp01050079): 第1教学周已占2节; 第2教学周已占8节</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -9043,67 +9047,67 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>61921003.001</t>
+          <t>150130580.006</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>职场礼仪与高情商沟通</t>
+          <t>专项4</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=5.5</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=280.0 | 教室类型名称=固定桌椅多媒体</t>
+          <t>课程行校区=南校区 | 课容量=13.0</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>教室静态不可行</t>
+          <t>时间偏好与周学时</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>⓪ 教室预筛</t>
+          <t>⓪ 日模式生成</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
+          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>ZXS=2.0 | Prefer=无</t>
+          <t>ZXS=5.5 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
+          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>二级</t>
+          <t>一级</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
+          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
+          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>新晓冰(xkp01090150): 第13教学周已占4节; 第14教学周已占4节</t>
+          <t>新艳华(xkp01050031): 第1教学周已占4节; 第2教学周已占10节</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -9112,136 +9116,132 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>62221001.002</t>
+          <t>150130580.007</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>侦探之旅：从柯南道尔到AI司鉴</t>
+          <t>专项4</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>课程行校区=北校区 | 课容量=210.0</t>
+          <t>课程行校区=南校区 | 课容量=13.0</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>教室静态不可行</t>
+          <t>时间偏好与周学时</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>⓪ 教室预筛</t>
+          <t>⓪ 日模式生成</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
+          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>ZXS=2.0 | Prefer=无</t>
+          <t>ZXS=6.0 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
+          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>二级</t>
+          <t>一级</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
+          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>新蒙(xkp01231016): 第9教学周已占2节; 第10教学周已占2节</t>
-        </is>
-      </c>
+          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>081010790.001</t>
+          <t>150130580.008</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>高电压技术</t>
+          <t>专项4</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=5.5</t>
+          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=304.0 | 教室类型名称=固定桌椅多媒体</t>
+          <t>课程行校区=南校区 | 课容量=14.0</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>教室静态不可行</t>
+          <t>时间偏好与周学时</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>⓪ 教室预筛</t>
+          <t>⓪ 日模式生成</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
+          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>ZXS=5.5 | Prefer=无</t>
+          <t>ZXS=6.0 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
+          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>二级</t>
+          <t>一级</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
+          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
+          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>新来军(xkp01060067): 第6教学周已占6节; 第7教学周已占6节</t>
+          <t>新爱增(xkp01230004): 第1教学周已占2节; 第2教学周已占2节</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -9250,132 +9250,136 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>081010810.001</t>
+          <t>150130680.002</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>现代电气控制技术与PLC</t>
+          <t>专项2</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
+          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=270.0 | 教室类型名称=固定桌椅多媒体</t>
+          <t>课程行校区=南校区 | 课容量=11.0</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>教室静态不可行</t>
+          <t>时间偏好与周学时</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>⓪ 教室预筛</t>
+          <t>⓪ 日模式生成</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
+          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>ZXS=4.0 | Prefer=无</t>
+          <t>ZXS=6.0 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
+          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>二级</t>
+          <t>一级</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
+          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr"/>
+          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>新正龙(xkp01050039): 第1教学周已占6节; 第2教学周已占18节</t>
+        </is>
+      </c>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>090010740.002</t>
+          <t>150130680.003</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>大数据分析技术</t>
+          <t>专项2</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
+          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>课程行校区=北校区 | 课容量=204.0</t>
+          <t>课程行校区=南校区 | 课容量=11.0</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>教室静态不可行</t>
+          <t>时间偏好与周学时</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>⓪ 教室预筛</t>
+          <t>⓪ 日模式生成</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
+          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>ZXS=4.0 | Prefer=无</t>
+          <t>ZXS=6.0 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
+          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>二级</t>
+          <t>一级</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
+          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
+          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>新朝生(xkp01070108): 第7教学周已占8节; 第8教学周已占8节</t>
+          <t>新海兵(xkp01050014): 第1教学周已占10节; 第2教学周已占10节</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -9384,67 +9388,67 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>091010020.001</t>
+          <t>150130680.004</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>算法分析与设计</t>
+          <t>专项2</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
+          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>课程行校区=北校区 | 课容量=245.0</t>
+          <t>课程行校区=南校区 | 课容量=10.0</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>教室静态不可行</t>
+          <t>时间偏好与周学时</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>⓪ 教室预筛</t>
+          <t>⓪ 日模式生成</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
+          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>ZXS=4.0 | Prefer=无</t>
+          <t>ZXS=6.0 | Prefer=周一(6-7节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
+          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>二级</t>
+          <t>一级</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
+          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
+          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>新东(xkp01079355): 第9教学周已占8节; 第10教学周已占8节</t>
+          <t>新黎君(xkp01050034): 第1教学周已占2节; 第2教学周已占2节</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -9453,67 +9457,67 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>091017031.001</t>
+          <t>150130680.005</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>文献检索与科技论文写作</t>
+          <t>专项2</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
+          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=5.5</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>课程行校区=北校区 | 课容量=204.0</t>
+          <t>课程行校区=南校区 | 课容量=10.0</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>教室静态不可行</t>
+          <t>时间偏好与周学时</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>⓪ 教室预筛</t>
+          <t>⓪ 日模式生成</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
+          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>ZXS=4.0 | Prefer=无</t>
+          <t>ZXS=5.5 | Prefer=周一(6-7节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
+          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>二级</t>
+          <t>一级</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
+          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
+          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>新富凯(xkp01230450): 第13教学周已占8节; 第14教学周已占8节</t>
+          <t>新孝志(xkp01050019): 第1教学周已占8节; 第2教学周已占14节 | 新娟(xkp01050085): 第1教学周已占8节; 第2教学周已占8节</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -9522,112 +9526,116 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>091058011.001</t>
+          <t>150130680.006</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>软件新技术讲座</t>
+          <t>专项2</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
+          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=5.5</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>课程行校区=北校区 | 课容量=204.0</t>
+          <t>课程行校区=南校区 | 课容量=10.0</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>教室静态不可行</t>
+          <t>时间偏好与周学时</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>⓪ 教室预筛</t>
+          <t>⓪ 日模式生成</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
+          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>ZXS=4.0 | Prefer=无</t>
+          <t>ZXS=5.5 | Prefer=周一(6-7节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
+          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>二级</t>
+          <t>一级</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
+          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr"/>
+          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>新艳华(xkp01050031): 第1教学周已占4节; 第2教学周已占10节</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>110010321.001</t>
+          <t>150130700.001</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>高等代数2</t>
+          <t>私人教练指导</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Prefer_Time=周六全天；周日全天 | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=2条 | 禁止时段解析块=1段 | ZXS=8.0</t>
+          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=100.0 | 教室类型名称=固定桌椅多媒体</t>
+          <t>课程行校区=南校区 | 课容量=82.0</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>资源冲突或偏好过窄</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>① 偏好节次错位</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>ZXS=8.0 | Prefer=周六全天;周日全天 | unavail=周二(5-8节)</t>
+          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -9637,36 +9645,44 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1195（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新华伟(xkp01050027): 第1教学周已占2节; 第2教学周已占8节 | 新燕(xkp01050051): 第1教学周已占6节; 第2教学周已占6节 | 新燚(xkp01050067): 第1教学周已占4节; 第2教学周已占4节 | 新新海(xkp01050035): 第1教学周已占12节; 第2教学周已占12节</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>新杰(xkp01040124): 第3教学周已占10节; 第4教学周已占10节</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
+          <t>新华伟(xkp01050027): 第1教学周已占2节; 第2教学周已占8节 | 新燕(xkp01050051): 第1教学周已占6节; 第2教学周已占6节 | 新燚(xkp01050067): 第1教学周已占4节; 第2教学周已占4节 | 新新海(xkp01050035): 第1教学周已占12节; 第2教学周已占12节</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>偏好窗口外</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>偏好窗口外×1195</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>150010280.001</t>
+          <t>150130880.001</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>运动处方理论与应用</t>
+          <t>健身俱乐部经营与管理</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Prefer_Time=周五（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=1.9999999</t>
+          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周一全天；周二全天；周五全天 | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=3段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -9706,7 +9722,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1195（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新燚(xkp01050067): 第1教学周已占4节; 第2教学周已占4节</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1195（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新永新(xkp01050075): 第1教学周已占8节; 第2教学周已占14节</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9716,7 +9732,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>新燚(xkp01050067): 第1教学周已占4节; 第2教学周已占4节</t>
+          <t>新永新(xkp01050075): 第1教学周已占8节; 第2教学周已占14节</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9733,47 +9749,47 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>150130580.002</t>
+          <t>150140220.001</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>民间武术套路2</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
+          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=7.0</t>
+          <t>课程行校区=南校区 | 课容量=41.0</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>资源冲突或偏好过窄</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>① 偏好节次错位</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>ZXS=6.0 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
+          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -9783,36 +9799,40 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1810（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>新建营(xkp01050033): 第1教学周已占12节; 第2教学周已占18节</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>偏好窗口外</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>偏好窗口外×1810</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>150130580.003</t>
+          <t>150140470.002</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>武术竞赛与训练2</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
+          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -9822,27 +9842,27 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>资源冲突或偏好过窄</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>① 偏好节次错位</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>ZXS=6.0 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
+          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -9852,36 +9872,44 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1980（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>新毅新(xkp01050084): 第1教学周已占12节; 第2教学周已占12节</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
+          <t>新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>偏好窗口外</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>偏好窗口外×1980</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>150130580.004</t>
+          <t>150140470.003</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>武术竞赛与训练2</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
+          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -9891,27 +9919,27 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>资源冲突或偏好过窄</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>① 偏好节次错位</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>ZXS=6.0 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
+          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -9921,66 +9949,74 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1980（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>新军勇(xkp01050009): 第1教学周已占10节; 第2教学周已占10节</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
+          <t>新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>偏好窗口外</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>偏好窗口外×1980</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>150130580.005</t>
+          <t>150140470.004</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>武术竞赛与训练2</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
+          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=1.9999999</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=14.0</t>
+          <t>课程行校区=南校区 | 课容量=13.0</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>资源冲突或偏好过窄</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>① 偏好节次错位</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>ZXS=6.0 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
+          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -9990,66 +10026,74 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1980（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>新希丹(xkp01050079): 第1教学周已占2节; 第2教学周已占8节</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
+          <t>新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>偏好窗口外</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>偏好窗口外×1980</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>150130580.006</t>
+          <t>150140490.002</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>武术竞赛与训练4</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=5.5</t>
+          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=13.0</t>
+          <t>课程行校区=南校区 | 课容量=10.0</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>资源冲突或偏好过窄</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>① 偏好节次错位</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>ZXS=5.5 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
+          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -10059,66 +10103,74 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1985（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>新艳华(xkp01050031): 第1教学周已占4节; 第2教学周已占10节</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
+          <t>新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>偏好窗口外</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>偏好窗口外×1985</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>150130580.007</t>
+          <t>150140490.003</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>武术竞赛与训练4</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
+          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=13.0</t>
+          <t>课程行校区=南校区 | 课容量=10.0</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>资源冲突或偏好过窄</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>① 偏好节次错位</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>ZXS=6.0 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
+          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -10128,62 +10180,74 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1985（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
-        </is>
-      </c>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>偏好窗口外</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>偏好窗口外×1985</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>150130580.008</t>
+          <t>150140490.004</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>武术竞赛与训练4</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
+          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=14.0</t>
+          <t>课程行校区=南校区 | 课容量=10.0</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>资源冲突或偏好过窄</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>① 偏好节次错位</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>ZXS=6.0 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
+          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -10193,66 +10257,74 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1985（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>新爱增(xkp01230004): 第1教学周已占2节; 第2教学周已占2节</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
+          <t>新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>偏好窗口外</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>偏好窗口外×1985</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>150130680.002</t>
+          <t>150140570.001</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>专项2</t>
+          <t>散打2</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
+          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=11.0</t>
+          <t>课程行校区=南校区 | 课容量=21.0</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>资源冲突或偏好过窄</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>① 偏好节次错位</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>ZXS=6.0 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
+          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -10262,41 +10334,49 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1965（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新新豪(xkp01050087): 第1教学周已占6节; 第2教学周已占6节</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>新正龙(xkp01050039): 第1教学周已占6节; 第2教学周已占18节</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
+          <t>新新豪(xkp01050087): 第1教学周已占6节; 第2教学周已占6节</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>偏好窗口外</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>偏好窗口外×1965</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>150130680.003</t>
+          <t>150140670.002</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>专项2</t>
+          <t>专项3</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（3-4节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
+          <t>Prefer_Time=周二（1-2节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=4.0</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=11.0</t>
+          <t>课程行校区=南校区 | 课容量=14.0 | 教室类型名称=体育类专用</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -10316,7 +10396,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>ZXS=6.0 | Prefer=周一(3-4节) | unavail=周二(5-8节)</t>
+          <t>ZXS=4.0 | Prefer=周二(1-2节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -10341,7 +10421,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>新海兵(xkp01050014): 第1教学周已占10节; 第2教学周已占10节</t>
+          <t>新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
@@ -10350,22 +10430,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>150130680.004</t>
+          <t>150140670.003</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>专项2</t>
+          <t>专项3</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=6.0</t>
+          <t>Prefer_Time=周二（1-2节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=4.0</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=10.0</t>
+          <t>课程行校区=南校区 | 课容量=15.0 | 教室类型名称=体育类专用</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -10385,7 +10465,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>ZXS=6.0 | Prefer=周一(6-7节) | unavail=周二(5-8节)</t>
+          <t>ZXS=4.0 | Prefer=周二(1-2节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -10410,7 +10490,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>新黎君(xkp01050034): 第1教学周已占2节; 第2教学周已占2节</t>
+          <t>新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
@@ -10419,22 +10499,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>150130680.005</t>
+          <t>150140670.004</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>专项2</t>
+          <t>专项3</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=5.5</t>
+          <t>Prefer_Time=周二（1-2节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=3.9999998</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=10.0</t>
+          <t>课程行校区=南校区 | 课容量=14.0 | 教室类型名称=体育类专用</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -10454,7 +10534,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>ZXS=5.5 | Prefer=周一(6-7节) | unavail=周二(5-8节)</t>
+          <t>ZXS=3.9999998 | Prefer=周二(1-2节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -10479,7 +10559,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>新孝志(xkp01050019): 第1教学周已占8节; 第2教学周已占14节 | 新娟(xkp01050085): 第1教学周已占8节; 第2教学周已占8节</t>
+          <t>新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -10488,22 +10568,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>150130680.006</t>
+          <t>150140760.002</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>专项2</t>
+          <t>专项5</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=5.5</t>
+          <t>Prefer_Time=周二（1-2节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=4.0</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=10.0</t>
+          <t>课程行校区=南校区 | 课容量=14.0</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -10523,7 +10603,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>ZXS=5.5 | Prefer=周一(6-7节) | unavail=周二(5-8节)</t>
+          <t>ZXS=4.0 | Prefer=周二(1-2节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -10548,7 +10628,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>新艳华(xkp01050031): 第1教学周已占4节; 第2教学周已占10节</t>
+          <t>新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
@@ -10557,47 +10637,47 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>150130700.001</t>
+          <t>150140760.003</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>私人教练指导</t>
+          <t>专项5</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=周二（1-2节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=4.0</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=82.0</t>
+          <t>课程行校区=南校区 | 课容量=13.0</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>资源冲突或偏好过窄</t>
+          <t>时间偏好与周学时</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>① 偏好节次错位</t>
+          <t>⓪ 日模式生成</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
+          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
+          <t>ZXS=4.0 | Prefer=周二(1-2节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
+          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -10607,74 +10687,66 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1195（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新华伟(xkp01050027): 第1教学周已占2节; 第2教学周已占8节 | 新燕(xkp01050051): 第1教学周已占6节; 第2教学周已占6节 | 新燚(xkp01050067): 第1教学周已占4节; 第2教学周已占4节 | 新新海(xkp01050035): 第1教学周已占12节; 第2教学周已占12节</t>
+          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
+          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>新华伟(xkp01050027): 第1教学周已占2节; 第2教学周已占8节 | 新燕(xkp01050051): 第1教学周已占6节; 第2教学周已占6节 | 新燚(xkp01050067): 第1教学周已占4节; 第2教学周已占4节 | 新新海(xkp01050035): 第1教学周已占12节; 第2教学周已占12节</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>偏好窗口外</t>
-        </is>
-      </c>
-      <c r="O139" t="inlineStr">
-        <is>
-          <t>偏好窗口外×1195</t>
-        </is>
-      </c>
+          <t>新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>150130880.001</t>
+          <t>150140760.004</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>健身俱乐部经营与管理</t>
+          <t>专项5</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周一全天；周二全天；周五全天 | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=3段 | ZXS=2.0</t>
+          <t>Prefer_Time=周二（1-2节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=4.0</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=82.0</t>
+          <t>课程行校区=南校区 | 课容量=13.0</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>资源冲突或偏好过窄</t>
+          <t>时间偏好与周学时</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>① 偏好节次错位</t>
+          <t>⓪ 日模式生成</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
+          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
+          <t>ZXS=4.0 | Prefer=周二(1-2节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
+          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -10684,44 +10756,36 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1195（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新永新(xkp01050075): 第1教学周已占8节; 第2教学周已占8节</t>
+          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
+          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>新永新(xkp01050075): 第1教学周已占8节; 第2教学周已占8节</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>偏好窗口外</t>
-        </is>
-      </c>
-      <c r="O140" t="inlineStr">
-        <is>
-          <t>偏好窗口外×1195</t>
-        </is>
-      </c>
+          <t>新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>150140220.001</t>
+          <t>151130120.001</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>民间武术套路2</t>
+          <t>乒乓球</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=周二（1-2节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=4.0</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -10731,27 +10795,27 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>资源冲突或偏好过窄</t>
+          <t>时间偏好与周学时</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>① 偏好节次错位</t>
+          <t>⓪ 日模式生成</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
+          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
+          <t>ZXS=4.0 | Prefer=周二(1-2节) | unavail=周二(5-8节)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
+          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -10761,45 +10825,37 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1810（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。</t>
+          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
+          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
         </is>
       </c>
       <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>偏好窗口外</t>
-        </is>
-      </c>
-      <c r="O141" t="inlineStr">
-        <is>
-          <t>偏好窗口外×1810</t>
-        </is>
-      </c>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>150140470.002</t>
+          <t>160060320.047</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>武术竞赛与训练2</t>
+          <t>声乐4</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=14.0</t>
+          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -10809,22 +10865,22 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>① 偏好节次错位</t>
+          <t>③ 教师时段饱和</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
+          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
+          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -10834,7 +10890,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1980（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10844,7 +10900,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10854,29 +10910,29 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>偏好窗口外×1980</t>
+          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>150140470.003</t>
+          <t>160060320.048</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>武术竞赛与训练2</t>
+          <t>声乐4</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=14.0</t>
+          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -10886,22 +10942,22 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>① 偏好节次错位</t>
+          <t>③ 教师时段饱和</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
+          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
+          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -10911,7 +10967,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1980（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10921,7 +10977,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10931,29 +10987,29 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>偏好窗口外×1980</t>
+          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>150140470.004</t>
+          <t>160060320.049</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>武术竞赛与训练2</t>
+          <t>声乐4</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=1.9999999</t>
+          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=13.0</t>
+          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -10963,22 +11019,22 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>① 偏好节次错位</t>
+          <t>③ 教师时段饱和</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
+          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
+          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -10988,7 +11044,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1980（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10998,7 +11054,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -11008,29 +11064,29 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>偏好窗口外×1980</t>
+          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>150140490.002</t>
+          <t>160060320.050</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>武术竞赛与训练4</t>
+          <t>声乐4</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=10.0</t>
+          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -11040,22 +11096,22 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>① 偏好节次错位</t>
+          <t>③ 教师时段饱和</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
+          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
+          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -11065,7 +11121,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1985（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -11075,7 +11131,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -11085,29 +11141,29 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>偏好窗口外×1985</t>
+          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>150140490.003</t>
+          <t>160060320.051</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>武术竞赛与训练4</t>
+          <t>声乐4</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=10.0</t>
+          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -11117,22 +11173,22 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>① 偏好节次错位</t>
+          <t>③ 教师时段饱和</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
+          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
+          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -11142,7 +11198,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1985（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -11152,7 +11208,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -11162,29 +11218,29 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>偏好窗口外×1985</t>
+          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>150140490.004</t>
+          <t>160060320.052</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>武术竞赛与训练4</t>
+          <t>声乐4</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=10.0</t>
+          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -11194,22 +11250,22 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>① 偏好节次错位</t>
+          <t>③ 教师时段饱和</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
+          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
+          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -11219,7 +11275,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1985（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11229,7 +11285,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11239,29 +11295,29 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>偏好窗口外×1985</t>
+          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>150140570.001</t>
+          <t>160060340.047</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>散打2</t>
+          <t>声乐6</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Prefer_Time=周一（6-7节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=2.0</t>
+          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=21.0</t>
+          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -11271,22 +11327,22 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>① 偏好节次错位</t>
+          <t>③ 教师时段饱和</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>偏好节次窗口与标准2节连排格子(1-2/3-4/5-6/7-8)不对齐</t>
+          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Prefer=周X(6-7节) 跨块边界，放不下标准2节块</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>把偏好改成对齐网格的相邻块，如 6-7节 → 5-6节 或 7-8节</t>
+          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -11296,7 +11352,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=1965（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=0（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 新新豪(xkp01050087): 第1教学周已占6节; 第2教学周已占6节</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11306,7 +11362,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>新新豪(xkp01050087): 第1教学周已占6节; 第2教学周已占6节</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11316,54 +11372,54 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>偏好窗口外×1965</t>
+          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>150140670.002</t>
+          <t>160060340.048</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>专项3</t>
+          <t>声乐6</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Prefer_Time=周二（1-2节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=4.0</t>
+          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=14.0 | 教室类型名称=体育类专用</t>
+          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>资源冲突或偏好过窄</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>③ 教师时段饱和</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>ZXS=4.0 | Prefer=周二(1-2节) | unavail=周二(5-8节)</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -11373,66 +11429,74 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>偏好窗口外</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>150140670.003</t>
+          <t>160060340.049</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>专项3</t>
+          <t>声乐6</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Prefer_Time=周二（1-2节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=4.0</t>
+          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=15.0 | 教室类型名称=体育类专用</t>
+          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>资源冲突或偏好过窄</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>③ 教师时段饱和</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>ZXS=4.0 | Prefer=周二(1-2节) | unavail=周二(5-8节)</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -11442,66 +11506,74 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
-      <c r="O150" t="inlineStr"/>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>偏好窗口外</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>150140670.004</t>
+          <t>160060340.050</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>专项3</t>
+          <t>声乐6</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Prefer_Time=周二（1-2节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=3.9999998</t>
+          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=14.0 | 教室类型名称=体育类专用</t>
+          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>资源冲突或偏好过窄</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>③ 教师时段饱和</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>ZXS=3.9999998 | Prefer=周二(1-2节) | unavail=周二(5-8节)</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -11511,66 +11583,74 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr"/>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>偏好窗口外</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>150140760.002</t>
+          <t>160060340.051</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>专项5</t>
+          <t>声乐6</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Prefer_Time=周二（1-2节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=4.0</t>
+          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=14.0</t>
+          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>资源冲突或偏好过窄</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>③ 教师时段饱和</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>ZXS=4.0 | Prefer=周二(1-2节) | unavail=周二(5-8节)</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -11580,66 +11660,74 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>新亚杰(xkp01050024): 第1教学周已占4节; 第2教学周已占10节</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr"/>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>偏好窗口外</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>150140760.003</t>
+          <t>160060360.040</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>专项5</t>
+          <t>声乐8</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Prefer_Time=周二（1-2节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=4.0</t>
+          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=13.0</t>
+          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>资源冲突或偏好过窄</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>③ 教师时段饱和</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>ZXS=4.0 | Prefer=周二(1-2节) | unavail=周二(5-8节)</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -11649,66 +11737,74 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=405（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>新守惠(xkp01050069): 第1教学周已占4节; 第2教学周已占4节</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr"/>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>偏好窗口外</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>偏好窗口外×405；教室占用×191；教师占用×79</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>150140760.004</t>
+          <t>160060360.041</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>专项5</t>
+          <t>声乐8</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Prefer_Time=周二（1-2节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=4.0</t>
+          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=13.0</t>
+          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>资源冲突或偏好过窄</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>③ 教师时段饱和</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>ZXS=4.0 | Prefer=周二(1-2节) | unavail=周二(5-8节)</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -11718,66 +11814,74 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=405（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>新庆丰(xkp01050011): 第1教学周已占4节; 第2教学周已占4节</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr"/>
-      <c r="O154" t="inlineStr"/>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>偏好窗口外</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>偏好窗口外×405；教室占用×191；教师占用×79</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>151130120.001</t>
+          <t>160060360.042</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>乒乓球</t>
+          <t>声乐8</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Prefer_Time=周二（1-2节） | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=1条 | 禁止时段解析块=1段 | ZXS=4.0</t>
+          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=41.0</t>
+          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>时间偏好与周学时</t>
+          <t>资源冲突或偏好过窄</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>⓪ 日模式生成</t>
+          <t>③ 教师时段饱和</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>偏好与ZXS不自洽(生成不出合法日模式)</t>
+          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>ZXS=4.0 | Prefer=周二(1-2节) | unavail=周二(5-8节)</t>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>核对 ZXS 与偏好组总学时是否相等；如 ZXS=7 却只偏好周末全天则需改偏好或拆班</t>
+          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -11787,37 +11891,49 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>无法生成任何上课日模式（偏好组与 ZXS 不匹配或 preferred_options 过滤过严）</t>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=405（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>放宽偏好或调整 ZXS / 偏好组总学时</t>
-        </is>
-      </c>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
-      <c r="O155" t="inlineStr"/>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>偏好窗口外</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>偏好窗口外×405；教室占用×191；教师占用×79</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>160060320.047</t>
+          <t>160060430.001</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>声乐4</t>
+          <t>声乐艺术史及作品欣赏2</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
+          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=2.0</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
+          <t>课程行校区=南校区 | 课容量=100.0 | 教室类型名称=艺术类专用</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -11827,44 +11943,44 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>③ 教师时段饱和</t>
+          <t>② 教室时段占用</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
+          <t>教室时段被占满(已通过时间窗口)</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
+          <t>ZXS=2.0 | Prefer=周三(5-8节)、周四(5-8节)、周五(5-8节)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>扩候选教室 / 错峰该教室既有占用</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>一级</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=18（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=12（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×12。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
           <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>一级</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
-        </is>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
       <c r="N156" t="inlineStr">
         <is>
           <t>偏好窗口外</t>
@@ -11872,19 +11988,19 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
+          <t>偏好窗口外×18；教室占用×12</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>160060320.048</t>
+          <t>16502002.041</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>声乐4</t>
+          <t>声乐2</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -11956,12 +12072,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>160060320.049</t>
+          <t>16502002.042</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>声乐4</t>
+          <t>声乐2</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -12033,12 +12149,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>160060320.050</t>
+          <t>16502002.043</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>声乐4</t>
+          <t>声乐2</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -12110,12 +12226,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>160060320.051</t>
+          <t>16502002.044</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>声乐4</t>
+          <t>声乐2</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -12187,1275 +12303,197 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>160060320.052</t>
+          <t>271010080.001</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>声乐4</t>
+          <t>Java EE开发技术</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
+          <t>Prefer_Time=周三全天；周四全天 | unavailable_Time=周一全天；周二全天；周五全天 | 解析后 preferred_groups=0组 | preferred_options=2条 | 禁止时段解析块=3段 | ZXS=3.5</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
+          <t>课程行校区=北校区 | 课容量=204.0</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>资源冲突或偏好过窄</t>
+          <t>教室静态不可行</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>③ 教师时段饱和</t>
+          <t>⓪ 教室预筛</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
+          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+          <t>ZXS=3.5 | Prefer=周三全天;周四全天</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
+          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>一级</t>
+          <t>二级</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
-        </is>
-      </c>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr">
-        <is>
-          <t>偏好窗口外</t>
-        </is>
-      </c>
-      <c r="O161" t="inlineStr">
-        <is>
-          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
-        </is>
-      </c>
+          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>160060340.047</t>
+          <t>271010091.002</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>声乐6</t>
+          <t>移动开发技术</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
+          <t>课程行校区=北校区 | 课容量=204.0</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>资源冲突或偏好过窄</t>
+          <t>教室静态不可行</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>③ 教师时段饱和</t>
+          <t>⓪ 教室预筛</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
+          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+          <t>ZXS=4.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
+          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>一级</t>
+          <t>二级</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
-        </is>
-      </c>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr">
-        <is>
-          <t>偏好窗口外</t>
-        </is>
-      </c>
-      <c r="O162" t="inlineStr">
-        <is>
-          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
-        </is>
-      </c>
+          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>160060340.048</t>
+          <t>271030050.001</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>声乐6</t>
+          <t>网络编程提高</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
+          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
+          <t>课程行校区=北校区 | 课容量=247.0</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>资源冲突或偏好过窄</t>
+          <t>教室静态不可行</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>③ 教师时段饱和</t>
+          <t>⓪ 教室预筛</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
+          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+          <t>ZXS=4.0 | Prefer=无</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
+          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>一级</t>
+          <t>二级</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
+          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
-        </is>
-      </c>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>偏好窗口外</t>
-        </is>
-      </c>
-      <c r="O163" t="inlineStr">
-        <is>
-          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>160060340.049</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>声乐6</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>资源冲突或偏好过窄</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>③ 教师时段饱和</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>一级</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
-        </is>
-      </c>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>偏好窗口外</t>
-        </is>
-      </c>
-      <c r="O164" t="inlineStr">
-        <is>
-          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>160060340.050</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>声乐6</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>资源冲突或偏好过窄</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>③ 教师时段饱和</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>一级</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
-        </is>
-      </c>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>偏好窗口外</t>
-        </is>
-      </c>
-      <c r="O165" t="inlineStr">
-        <is>
-          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>160060340.051</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>声乐6</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>资源冲突或偏好过窄</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>③ 教师时段饱和</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>一级</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
-        </is>
-      </c>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>偏好窗口外</t>
-        </is>
-      </c>
-      <c r="O166" t="inlineStr">
-        <is>
-          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>160060360.040</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>声乐8</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=2.0</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>资源冲突或偏好过窄</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>③ 教师时段饱和</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>一级</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=405（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
-        </is>
-      </c>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="N167" t="inlineStr">
-        <is>
-          <t>偏好窗口外</t>
-        </is>
-      </c>
-      <c r="O167" t="inlineStr">
-        <is>
-          <t>偏好窗口外×405；教室占用×191；教师占用×79</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>160060360.041</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>声乐8</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=2.0</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>资源冲突或偏好过窄</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>③ 教师时段饱和</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>一级</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=405（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
-        </is>
-      </c>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>偏好窗口外</t>
-        </is>
-      </c>
-      <c r="O168" t="inlineStr">
-        <is>
-          <t>偏好窗口外×405；教室占用×191；教师占用×79</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>160060360.042</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>声乐8</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=2.0</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>资源冲突或偏好过窄</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>③ 教师时段饱和</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>一级</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=405（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
-        </is>
-      </c>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>偏好窗口外</t>
-        </is>
-      </c>
-      <c r="O169" t="inlineStr">
-        <is>
-          <t>偏好窗口外×405；教室占用×191；教师占用×79</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>160060430.001</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>声乐艺术史及作品欣赏2</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=2.0</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>课程行校区=南校区 | 课容量=100.0 | 教室类型名称=艺术类专用</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>资源冲突或偏好过窄</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>② 教室时段占用</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>教室时段被占满(已通过时间窗口)</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>ZXS=2.0 | Prefer=周三(5-8节)、周四(5-8节)、周五(5-8节)</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>扩候选教室 / 错峰该教室既有占用</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>一级</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=18（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=12（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×12。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
-        </is>
-      </c>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>偏好窗口外</t>
-        </is>
-      </c>
-      <c r="O170" t="inlineStr">
-        <is>
-          <t>偏好窗口外×18；教室占用×12</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>16502002.041</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>声乐2</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>资源冲突或偏好过窄</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>③ 教师时段饱和</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>一级</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
-        </is>
-      </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>偏好窗口外</t>
-        </is>
-      </c>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>16502002.042</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>声乐2</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>资源冲突或偏好过窄</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>③ 教师时段饱和</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>一级</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
-        </is>
-      </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>偏好窗口外</t>
-        </is>
-      </c>
-      <c r="O172" t="inlineStr">
-        <is>
-          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>16502002.043</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>声乐2</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>资源冲突或偏好过窄</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>③ 教师时段饱和</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>一级</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
-        </is>
-      </c>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr">
-        <is>
-          <t>偏好窗口外</t>
-        </is>
-      </c>
-      <c r="O173" t="inlineStr">
-        <is>
-          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>16502002.044</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>声乐2</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Prefer_Time=周三（5-8节）、周四（5-8节）、周五（5-8节） | unavailable_Time=周一全天；周二全天；周三（1-4节）；周四（1-4节）；周五（1-4节） | 解析后 preferred_groups=0组 | preferred_options=3条 | 禁止时段解析块=5段 | ZXS=1.0</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>课程行校区=南校区 | 课容量=1.0 | 教室类型名称=艺术类专用</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>资源冲突或偏好过窄</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>③ 教师时段饱和</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>教师时段饱和(一对一/带班过多，窗口内被占满)</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>减少该教师任务量 / 放宽偏好窗口 / 拆分一对一课到其它时段</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>一级</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>在当前全校占用与偏好下，枚举时段方案数为 0（教师/班级/教室时间重叠或偏好窗口无法容纳连排）。下列「枚举拒绝构成」为在所有候选教室×日模式下试探候选节次时各拒绝原因的累计次数，用于判断矛盾主要来自哪类约束（非唯一因果）。 首要矛盾（单项次数最多）：偏好窗口外。 【枚举顺序说明】对每个候选起点依次判定：偏好窗口/禁止时段 → 教室空闲 → 教师空闲 → 班级空闲。只有通过前几步的候选才会计入后续拒绝类型；故「首要枚举冲突」不等于业务上的唯一根因。 时间规则类合计=540（偏好窗口外/禁止/日模式不匹配/分段边界）；资源占用类合计=270（教室/教师/班级）。 累计时间规则拒绝更高；但若「教师占用摘要」显示多位教师已近乎满课，仍常为偏好窗口内无共同空闲。不宜仅凭「偏好窗口外」字样断定仅需改 Prefer_Time。 资源侧枚举构成：教室占用×191；教师占用×79。 新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>对照枚举构成：教室占用高→扩候选教室/错峰教室资源；教师占用高→减任务或协调其它课；班级占用高→调整班级课表；偏好窗口外/禁止高→放宽 Prefer_Time 或 unavailable_Time；日模式不匹配→核对偏好组与 ZXS。多教师团队课需结合「教师占用摘要」一起看。</t>
-        </is>
-      </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>新旋(xkp01200395): 第1教学周已占7节; 第2教学周已占11节</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>偏好窗口外</t>
-        </is>
-      </c>
-      <c r="O174" t="inlineStr">
-        <is>
-          <t>偏好窗口外×540；教室占用×191；教师占用×79</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>271010080.001</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Java EE开发技术</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Prefer_Time=周三全天；周四全天 | unavailable_Time=周一全天；周二全天；周五全天 | 解析后 preferred_groups=0组 | preferred_options=2条 | 禁止时段解析块=3段 | ZXS=3.5</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>课程行校区=北校区 | 课容量=204.0</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>教室静态不可行</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>⓪ 教室预筛</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>ZXS=3.5 | Prefer=周三全天;周四全天</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>二级</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
-        </is>
-      </c>
-      <c r="L175" t="inlineStr">
-        <is>
           <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
         </is>
       </c>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>271010091.002</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>移动开发技术</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>课程行校区=北校区 | 课容量=204.0</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>教室静态不可行</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>⓪ 教室预筛</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>ZXS=4.0 | Prefer=无</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>二级</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
-        </is>
-      </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
-        </is>
-      </c>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>271030050.001</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>网络编程提高</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Prefer_Time=(空) | unavailable_Time=周二(5-8节） | 解析后 preferred_groups=0组 | preferred_options=0条 | 禁止时段解析块=1段 | ZXS=4.0</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>课程行校区=北校区 | 课容量=247.0</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>教室静态不可行</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>⓪ 教室预筛</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>教室静态不可行(容量/类型预筛无匹配教室)</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>ZXS=4.0 | Prefer=无</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>扩候选教室池 / 放宽教室类型或容量匹配 / 错峰教室资源</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>二级</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>校区/容量/类型/指定教室导致无任何候选教室</t>
-        </is>
-      </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>调整 SKXQ、KRL、教室类型或指定教室字段</t>
-        </is>
-      </c>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
-      <c r="O177" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
